--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_building_materials.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_building_materials.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09173049850485661</v>
+        <v>0.09153492225859446</v>
       </c>
       <c r="C2">
-        <v>1024.376418801764</v>
+        <v>1016.741138053274</v>
       </c>
       <c r="D2">
-        <v>975.0764188017637</v>
+        <v>979.2461380532741</v>
       </c>
       <c r="E2">
-        <v>-506.8</v>
+        <v>-494.995</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.805</v>
       </c>
       <c r="G2">
         <v>49.3</v>
@@ -1451,28 +1451,28 @@
         <v>157.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5937914999999999</v>
       </c>
       <c r="N2">
-        <v>157.3</v>
+        <v>156.7062085</v>
       </c>
       <c r="O2">
-        <v>39.325</v>
+        <v>39.176552125</v>
       </c>
       <c r="P2">
-        <v>117.975</v>
+        <v>117.529656375</v>
       </c>
       <c r="Q2">
-        <v>163.175</v>
+        <v>162.729656375</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09173049850485661</v>
+        <v>0.09207845682686309</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9275896529086805</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>264.9078001284963</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09153492225859446</v>
+        <v>0.09133934601233233</v>
       </c>
       <c r="C3">
-        <v>1016.741138053274</v>
+        <v>1009.141672401424</v>
       </c>
       <c r="D3">
-        <v>979.2461380532741</v>
+        <v>983.4516724014239</v>
       </c>
       <c r="E3">
-        <v>-494.995</v>
+        <v>-483.19</v>
       </c>
       <c r="F3">
-        <v>11.805</v>
+        <v>23.61</v>
       </c>
       <c r="G3">
         <v>49.3</v>
@@ -1533,28 +1533,28 @@
         <v>157.3</v>
       </c>
       <c r="M3">
-        <v>0.5937914999999999</v>
+        <v>1.187583</v>
       </c>
       <c r="N3">
-        <v>156.7062085</v>
+        <v>156.112417</v>
       </c>
       <c r="O3">
-        <v>39.176552125</v>
+        <v>39.02810425000001</v>
       </c>
       <c r="P3">
-        <v>117.529656375</v>
+        <v>117.08431275</v>
       </c>
       <c r="Q3">
-        <v>162.729656375</v>
+        <v>162.28431275</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09207845682686309</v>
+        <v>0.09243351633911462</v>
       </c>
       <c r="T3">
-        <v>0.9275896529086805</v>
+        <v>0.934706345043932</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>264.9078001284963</v>
+        <v>132.4539000642482</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09133934601233233</v>
+        <v>0.09114376976607018</v>
       </c>
       <c r="C4">
-        <v>1009.141672401424</v>
+        <v>1001.57848527805</v>
       </c>
       <c r="D4">
-        <v>983.4516724014239</v>
+        <v>987.6934852780504</v>
       </c>
       <c r="E4">
-        <v>-483.19</v>
+        <v>-471.385</v>
       </c>
       <c r="F4">
-        <v>23.61</v>
+        <v>35.415</v>
       </c>
       <c r="G4">
         <v>49.3</v>
@@ -1615,28 +1615,28 @@
         <v>157.3</v>
       </c>
       <c r="M4">
-        <v>1.187583</v>
+        <v>1.7813745</v>
       </c>
       <c r="N4">
-        <v>156.112417</v>
+        <v>155.5186255</v>
       </c>
       <c r="O4">
-        <v>39.02810425000001</v>
+        <v>38.879656375</v>
       </c>
       <c r="P4">
-        <v>117.08431275</v>
+        <v>116.638969125</v>
       </c>
       <c r="Q4">
-        <v>162.28431275</v>
+        <v>161.838969125</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09243351633911462</v>
+        <v>0.09279589666605173</v>
       </c>
       <c r="T4">
-        <v>0.934706345043932</v>
+        <v>0.9419697730994978</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>132.4539000642482</v>
+        <v>88.30260004283211</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09114376976607018</v>
+        <v>0.09094819351980804</v>
       </c>
       <c r="C5">
-        <v>1001.57848527805</v>
+        <v>994.0520481451006</v>
       </c>
       <c r="D5">
-        <v>987.6934852780504</v>
+        <v>991.9720481451006</v>
       </c>
       <c r="E5">
-        <v>-471.385</v>
+        <v>-459.58</v>
       </c>
       <c r="F5">
-        <v>35.415</v>
+        <v>47.22</v>
       </c>
       <c r="G5">
         <v>49.3</v>
@@ -1697,28 +1697,28 @@
         <v>157.3</v>
       </c>
       <c r="M5">
-        <v>1.7813745</v>
+        <v>2.375166</v>
       </c>
       <c r="N5">
-        <v>155.5186255</v>
+        <v>154.924834</v>
       </c>
       <c r="O5">
-        <v>38.879656375</v>
+        <v>38.7312085</v>
       </c>
       <c r="P5">
-        <v>116.638969125</v>
+        <v>116.1936255</v>
       </c>
       <c r="Q5">
-        <v>161.838969125</v>
+        <v>161.3936255</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09279589666605173</v>
+        <v>0.09316582658313338</v>
       </c>
       <c r="T5">
-        <v>0.9419697730994978</v>
+        <v>0.9493845225728882</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.30260004283211</v>
+        <v>66.22695003212408</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09094819351980804</v>
+        <v>0.0907526172735459</v>
       </c>
       <c r="C6">
-        <v>994.0520481451006</v>
+        <v>986.5628406693182</v>
       </c>
       <c r="D6">
-        <v>991.9720481451006</v>
+        <v>996.2878406693183</v>
       </c>
       <c r="E6">
-        <v>-459.58</v>
+        <v>-447.775</v>
       </c>
       <c r="F6">
-        <v>47.22</v>
+        <v>59.02500000000001</v>
       </c>
       <c r="G6">
         <v>49.3</v>
@@ -1779,28 +1779,28 @@
         <v>157.3</v>
       </c>
       <c r="M6">
-        <v>2.375166</v>
+        <v>2.9689575</v>
       </c>
       <c r="N6">
-        <v>154.924834</v>
+        <v>154.3310425</v>
       </c>
       <c r="O6">
-        <v>38.7312085</v>
+        <v>38.58276062500001</v>
       </c>
       <c r="P6">
-        <v>116.1936255</v>
+        <v>115.748281875</v>
       </c>
       <c r="Q6">
-        <v>161.3936255</v>
+        <v>160.948281875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09316582658313338</v>
+        <v>0.09354354449846937</v>
       </c>
       <c r="T6">
-        <v>0.9493845225728882</v>
+        <v>0.956955372035192</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.22695003212408</v>
+        <v>52.98156002569926</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0907526172735459</v>
+        <v>0.09055704102728375</v>
       </c>
       <c r="C7">
-        <v>986.5628406693182</v>
+        <v>979.1113509015062</v>
       </c>
       <c r="D7">
-        <v>996.2878406693183</v>
+        <v>1000.641350901506</v>
       </c>
       <c r="E7">
-        <v>-447.775</v>
+        <v>-435.97</v>
       </c>
       <c r="F7">
-        <v>59.02500000000001</v>
+        <v>70.83000000000001</v>
       </c>
       <c r="G7">
         <v>49.3</v>
@@ -1861,28 +1861,28 @@
         <v>157.3</v>
       </c>
       <c r="M7">
-        <v>2.9689575</v>
+        <v>3.562749000000001</v>
       </c>
       <c r="N7">
-        <v>154.3310425</v>
+        <v>153.737251</v>
       </c>
       <c r="O7">
-        <v>38.58276062500001</v>
+        <v>38.43431275</v>
       </c>
       <c r="P7">
-        <v>115.748281875</v>
+        <v>115.30293825</v>
       </c>
       <c r="Q7">
-        <v>160.948281875</v>
+        <v>160.50293825</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09354354449846937</v>
+        <v>0.09392929896519549</v>
       </c>
       <c r="T7">
-        <v>0.956955372035192</v>
+        <v>0.9646873034009489</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.98156002569926</v>
+        <v>44.15130002141604</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09055704102728375</v>
+        <v>0.09036146478102162</v>
       </c>
       <c r="C8">
-        <v>979.1113509015062</v>
+        <v>971.6980754605097</v>
       </c>
       <c r="D8">
-        <v>1000.641350901506</v>
+        <v>1005.03307546051</v>
       </c>
       <c r="E8">
-        <v>-435.97</v>
+        <v>-424.165</v>
       </c>
       <c r="F8">
-        <v>70.83</v>
+        <v>82.63499999999999</v>
       </c>
       <c r="G8">
         <v>49.3</v>
@@ -1943,28 +1943,28 @@
         <v>157.3</v>
       </c>
       <c r="M8">
-        <v>3.562749</v>
+        <v>4.156540499999999</v>
       </c>
       <c r="N8">
-        <v>153.737251</v>
+        <v>153.1434595</v>
       </c>
       <c r="O8">
-        <v>38.43431275</v>
+        <v>38.285864875</v>
       </c>
       <c r="P8">
-        <v>115.30293825</v>
+        <v>114.857594625</v>
       </c>
       <c r="Q8">
-        <v>160.50293825</v>
+        <v>160.057594625</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09392929896519549</v>
+        <v>0.09432334922690497</v>
       </c>
       <c r="T8">
-        <v>0.9646873034009489</v>
+        <v>0.9725855128605931</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.15130002141606</v>
+        <v>37.84397144692804</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09036146478102161</v>
+        <v>0.09016588853475949</v>
       </c>
       <c r="C9">
-        <v>971.6980754605099</v>
+        <v>964.3235197220699</v>
       </c>
       <c r="D9">
-        <v>1005.03307546051</v>
+        <v>1009.46351972207</v>
       </c>
       <c r="E9">
-        <v>-424.165</v>
+        <v>-412.36</v>
       </c>
       <c r="F9">
-        <v>82.63500000000001</v>
+        <v>94.44</v>
       </c>
       <c r="G9">
         <v>49.3</v>
@@ -2025,28 +2025,28 @@
         <v>157.3</v>
       </c>
       <c r="M9">
-        <v>4.1565405</v>
+        <v>4.750331999999999</v>
       </c>
       <c r="N9">
-        <v>153.1434595</v>
+        <v>152.549668</v>
       </c>
       <c r="O9">
-        <v>38.285864875</v>
+        <v>38.13741700000001</v>
       </c>
       <c r="P9">
-        <v>114.857594625</v>
+        <v>114.412251</v>
       </c>
       <c r="Q9">
-        <v>160.057594625</v>
+        <v>159.612251</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09432334922690497</v>
+        <v>0.09472596579865161</v>
       </c>
       <c r="T9">
-        <v>0.9725855128605931</v>
+        <v>0.9806554225258819</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.84397144692804</v>
+        <v>33.11347501606205</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09016588853475949</v>
+        <v>0.08997031228849733</v>
       </c>
       <c r="C10">
-        <v>964.3235197220699</v>
+        <v>956.9881980126905</v>
       </c>
       <c r="D10">
-        <v>1009.46351972207</v>
+        <v>1013.933198012691</v>
       </c>
       <c r="E10">
-        <v>-412.36</v>
+        <v>-400.555</v>
       </c>
       <c r="F10">
-        <v>94.44</v>
+        <v>106.245</v>
       </c>
       <c r="G10">
         <v>49.3</v>
@@ -2107,28 +2107,28 @@
         <v>157.3</v>
       </c>
       <c r="M10">
-        <v>4.750331999999999</v>
+        <v>5.344123499999999</v>
       </c>
       <c r="N10">
-        <v>152.549668</v>
+        <v>151.9558765</v>
       </c>
       <c r="O10">
-        <v>38.13741700000001</v>
+        <v>37.988969125</v>
       </c>
       <c r="P10">
-        <v>114.412251</v>
+        <v>113.966907375</v>
       </c>
       <c r="Q10">
-        <v>159.612251</v>
+        <v>159.166907375</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09472596579865161</v>
+        <v>0.0951374310862608</v>
       </c>
       <c r="T10">
-        <v>0.9806554225258819</v>
+        <v>0.9889026928431549</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.11347501606205</v>
+        <v>29.43420001427737</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08997031228849733</v>
+        <v>0.08977473604223518</v>
       </c>
       <c r="C11">
-        <v>956.9881980126905</v>
+        <v>949.6926338086769</v>
       </c>
       <c r="D11">
-        <v>1013.933198012691</v>
+        <v>1018.442633808677</v>
       </c>
       <c r="E11">
-        <v>-400.555</v>
+        <v>-388.75</v>
       </c>
       <c r="F11">
-        <v>106.245</v>
+        <v>118.05</v>
       </c>
       <c r="G11">
         <v>49.3</v>
@@ -2189,28 +2189,28 @@
         <v>157.3</v>
       </c>
       <c r="M11">
-        <v>5.344123499999999</v>
+        <v>5.937914999999999</v>
       </c>
       <c r="N11">
-        <v>151.9558765</v>
+        <v>151.362085</v>
       </c>
       <c r="O11">
-        <v>37.988969125</v>
+        <v>37.84052125</v>
       </c>
       <c r="P11">
-        <v>113.966907375</v>
+        <v>113.52156375</v>
       </c>
       <c r="Q11">
-        <v>159.166907375</v>
+        <v>158.72156375</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0951374310862608</v>
+        <v>0.09555804004692799</v>
       </c>
       <c r="T11">
-        <v>0.9889026928431549</v>
+        <v>0.9973332358341451</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.43420001427737</v>
+        <v>26.49078001284963</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08977473604223518</v>
+        <v>0.08957915979597304</v>
       </c>
       <c r="C12">
-        <v>949.6926338086769</v>
+        <v>942.4373599405144</v>
       </c>
       <c r="D12">
-        <v>1018.442633808677</v>
+        <v>1022.992359940514</v>
       </c>
       <c r="E12">
-        <v>-388.75</v>
+        <v>-376.9450000000001</v>
       </c>
       <c r="F12">
-        <v>118.05</v>
+        <v>129.855</v>
       </c>
       <c r="G12">
         <v>49.3</v>
@@ -2271,28 +2271,28 @@
         <v>157.3</v>
       </c>
       <c r="M12">
-        <v>5.937915</v>
+        <v>6.531706499999999</v>
       </c>
       <c r="N12">
-        <v>151.362085</v>
+        <v>150.7682935</v>
       </c>
       <c r="O12">
-        <v>37.84052125</v>
+        <v>37.692073375</v>
       </c>
       <c r="P12">
-        <v>113.52156375</v>
+        <v>113.076220125</v>
       </c>
       <c r="Q12">
-        <v>158.72156375</v>
+        <v>158.276220125</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09555804004692799</v>
+        <v>0.09598810089435174</v>
       </c>
       <c r="T12">
-        <v>0.9973332358341451</v>
+        <v>1.005953229229427</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.49078001284963</v>
+        <v>24.08252728440876</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08957915979597304</v>
+        <v>0.08938358354971092</v>
       </c>
       <c r="C13">
-        <v>942.4373599405144</v>
+        <v>935.2229188027471</v>
       </c>
       <c r="D13">
-        <v>1022.992359940514</v>
+        <v>1027.582918802747</v>
       </c>
       <c r="E13">
-        <v>-376.9450000000001</v>
+        <v>-365.14</v>
       </c>
       <c r="F13">
-        <v>129.855</v>
+        <v>141.66</v>
       </c>
       <c r="G13">
         <v>49.3</v>
@@ -2353,28 +2353,28 @@
         <v>157.3</v>
       </c>
       <c r="M13">
-        <v>6.531706499999999</v>
+        <v>7.125497999999999</v>
       </c>
       <c r="N13">
-        <v>150.7682935</v>
+        <v>150.174502</v>
       </c>
       <c r="O13">
-        <v>37.692073375</v>
+        <v>37.5436255</v>
       </c>
       <c r="P13">
-        <v>113.076220125</v>
+        <v>112.6308765</v>
       </c>
       <c r="Q13">
-        <v>158.276220125</v>
+        <v>157.8308765</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09598810089435174</v>
+        <v>0.09642793585194422</v>
       </c>
       <c r="T13">
-        <v>1.005953229229427</v>
+        <v>1.014769131565511</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.08252728440876</v>
+        <v>22.07565001070803</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08938358354971092</v>
+        <v>0.08918800730344875</v>
       </c>
       <c r="C14">
-        <v>935.2229188027471</v>
+        <v>928.0498625695351</v>
       </c>
       <c r="D14">
-        <v>1027.582918802747</v>
+        <v>1032.214862569535</v>
       </c>
       <c r="E14">
-        <v>-365.14</v>
+        <v>-353.335</v>
       </c>
       <c r="F14">
-        <v>141.66</v>
+        <v>153.465</v>
       </c>
       <c r="G14">
         <v>49.3</v>
@@ -2435,28 +2435,28 @@
         <v>157.3</v>
       </c>
       <c r="M14">
-        <v>7.125497999999999</v>
+        <v>7.719289499999999</v>
       </c>
       <c r="N14">
-        <v>150.174502</v>
+        <v>149.5807105</v>
       </c>
       <c r="O14">
-        <v>37.5436255</v>
+        <v>37.395177625</v>
       </c>
       <c r="P14">
-        <v>112.6308765</v>
+        <v>112.185532875</v>
       </c>
       <c r="Q14">
-        <v>157.8308765</v>
+        <v>157.385532875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09642793585194422</v>
+        <v>0.09687788195798708</v>
       </c>
       <c r="T14">
-        <v>1.014769131565511</v>
+        <v>1.023787698323114</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.07565001070803</v>
+        <v>20.37752308680741</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08918800730344875</v>
+        <v>0.08899243105718663</v>
       </c>
       <c r="C15">
-        <v>928.0498625695351</v>
+        <v>920.9187534160596</v>
       </c>
       <c r="D15">
-        <v>1032.214862569535</v>
+        <v>1036.88875341606</v>
       </c>
       <c r="E15">
-        <v>-353.335</v>
+        <v>-341.53</v>
       </c>
       <c r="F15">
-        <v>153.465</v>
+        <v>165.27</v>
       </c>
       <c r="G15">
         <v>49.3</v>
@@ -2517,28 +2517,28 @@
         <v>157.3</v>
       </c>
       <c r="M15">
-        <v>7.719289499999999</v>
+        <v>8.313081</v>
       </c>
       <c r="N15">
-        <v>149.5807105</v>
+        <v>148.986919</v>
       </c>
       <c r="O15">
-        <v>37.395177625</v>
+        <v>37.24672975</v>
       </c>
       <c r="P15">
-        <v>112.185532875</v>
+        <v>111.74018925</v>
       </c>
       <c r="Q15">
-        <v>157.385532875</v>
+        <v>156.94018925</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09687788195798708</v>
+        <v>0.0973382919269612</v>
       </c>
       <c r="T15">
-        <v>1.023787698323114</v>
+        <v>1.03301599919136</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.37752308680741</v>
+        <v>18.92198572346402</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08899243105718663</v>
+        <v>0.08879685481092449</v>
       </c>
       <c r="C16">
-        <v>920.9187534160596</v>
+        <v>913.8301637459849</v>
       </c>
       <c r="D16">
-        <v>1036.88875341606</v>
+        <v>1041.605163745985</v>
       </c>
       <c r="E16">
-        <v>-341.53</v>
+        <v>-329.725</v>
       </c>
       <c r="F16">
-        <v>165.27</v>
+        <v>177.075</v>
       </c>
       <c r="G16">
         <v>49.3</v>
@@ -2599,28 +2599,28 @@
         <v>157.3</v>
       </c>
       <c r="M16">
-        <v>8.313081</v>
+        <v>8.9068725</v>
       </c>
       <c r="N16">
-        <v>148.986919</v>
+        <v>148.3931275</v>
       </c>
       <c r="O16">
-        <v>37.24672975</v>
+        <v>37.098281875</v>
       </c>
       <c r="P16">
-        <v>111.74018925</v>
+        <v>111.294845625</v>
       </c>
       <c r="Q16">
-        <v>156.94018925</v>
+        <v>156.494845625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0973382919269612</v>
+        <v>0.09780953507167586</v>
       </c>
       <c r="T16">
-        <v>1.03301599919136</v>
+        <v>1.042461436550622</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.92198572346402</v>
+        <v>17.66052000856642</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08879685481092449</v>
+        <v>0.08860127856466234</v>
       </c>
       <c r="C17">
-        <v>913.8301637459849</v>
+        <v>906.7846764251436</v>
       </c>
       <c r="D17">
-        <v>1041.605163745985</v>
+        <v>1046.364676425144</v>
       </c>
       <c r="E17">
-        <v>-329.725</v>
+        <v>-317.92</v>
       </c>
       <c r="F17">
-        <v>177.075</v>
+        <v>188.88</v>
       </c>
       <c r="G17">
         <v>49.3</v>
@@ -2681,28 +2681,28 @@
         <v>157.3</v>
       </c>
       <c r="M17">
-        <v>8.906872499999999</v>
+        <v>9.500663999999999</v>
       </c>
       <c r="N17">
-        <v>148.3931275</v>
+        <v>147.799336</v>
       </c>
       <c r="O17">
-        <v>37.098281875</v>
+        <v>36.949834</v>
       </c>
       <c r="P17">
-        <v>111.294845625</v>
+        <v>110.849502</v>
       </c>
       <c r="Q17">
-        <v>156.494845625</v>
+        <v>156.049502</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09780953507167586</v>
+        <v>0.0982919982912647</v>
       </c>
       <c r="T17">
-        <v>1.042461436550622</v>
+        <v>1.052131765275582</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.66052000856642</v>
+        <v>16.55673750803102</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08860127856466234</v>
+        <v>0.0884057023184002</v>
       </c>
       <c r="C18">
-        <v>906.7846764251436</v>
+        <v>899.782885021664</v>
       </c>
       <c r="D18">
-        <v>1046.364676425144</v>
+        <v>1051.167885021664</v>
       </c>
       <c r="E18">
-        <v>-317.92</v>
+        <v>-306.115</v>
       </c>
       <c r="F18">
-        <v>188.88</v>
+        <v>200.685</v>
       </c>
       <c r="G18">
         <v>49.3</v>
@@ -2763,28 +2763,28 @@
         <v>157.3</v>
       </c>
       <c r="M18">
-        <v>9.500663999999999</v>
+        <v>10.0944555</v>
       </c>
       <c r="N18">
-        <v>147.799336</v>
+        <v>147.2055445</v>
       </c>
       <c r="O18">
-        <v>36.949834</v>
+        <v>36.801386125</v>
       </c>
       <c r="P18">
-        <v>110.849502</v>
+        <v>110.404158375</v>
       </c>
       <c r="Q18">
-        <v>156.049502</v>
+        <v>155.604158375</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0982919982912647</v>
+        <v>0.09878608713060266</v>
       </c>
       <c r="T18">
-        <v>1.052131765275582</v>
+        <v>1.062035113969817</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.55673750803102</v>
+        <v>15.58281177226449</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0884057023184002</v>
+        <v>0.08821012607213806</v>
       </c>
       <c r="C19">
-        <v>899.782885021664</v>
+        <v>892.825394052742</v>
       </c>
       <c r="D19">
-        <v>1051.167885021664</v>
+        <v>1056.015394052742</v>
       </c>
       <c r="E19">
-        <v>-306.115</v>
+        <v>-294.3099999999999</v>
       </c>
       <c r="F19">
-        <v>200.685</v>
+        <v>212.49</v>
       </c>
       <c r="G19">
         <v>49.3</v>
@@ -2845,28 +2845,28 @@
         <v>157.3</v>
       </c>
       <c r="M19">
-        <v>10.0944555</v>
+        <v>10.688247</v>
       </c>
       <c r="N19">
-        <v>147.2055445</v>
+        <v>146.611753</v>
       </c>
       <c r="O19">
-        <v>36.801386125</v>
+        <v>36.65293825000001</v>
       </c>
       <c r="P19">
-        <v>110.404158375</v>
+        <v>109.95881475</v>
       </c>
       <c r="Q19">
-        <v>155.604158375</v>
+        <v>155.15881475</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09878608713060266</v>
+        <v>0.09929222691724153</v>
       </c>
       <c r="T19">
-        <v>1.062035113969817</v>
+        <v>1.072180007754156</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.58281177226449</v>
+        <v>14.71710000713868</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08821012607213806</v>
+        <v>0.08801454982587592</v>
       </c>
       <c r="C20">
-        <v>892.825394052742</v>
+        <v>885.9128192382707</v>
       </c>
       <c r="D20">
-        <v>1056.015394052742</v>
+        <v>1060.907819238271</v>
       </c>
       <c r="E20">
-        <v>-294.3100000000001</v>
+        <v>-282.505</v>
       </c>
       <c r="F20">
-        <v>212.49</v>
+        <v>224.295</v>
       </c>
       <c r="G20">
         <v>49.3</v>
@@ -2927,28 +2927,28 @@
         <v>157.3</v>
       </c>
       <c r="M20">
-        <v>10.688247</v>
+        <v>11.2820385</v>
       </c>
       <c r="N20">
-        <v>146.611753</v>
+        <v>146.0179615</v>
       </c>
       <c r="O20">
-        <v>36.65293825000001</v>
+        <v>36.504490375</v>
       </c>
       <c r="P20">
-        <v>109.95881475</v>
+        <v>109.513471125</v>
       </c>
       <c r="Q20">
-        <v>155.15881475</v>
+        <v>154.713471125</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09929222691724153</v>
+        <v>0.09981086398256286</v>
       </c>
       <c r="T20">
-        <v>1.072180007754156</v>
+        <v>1.082575392743047</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.71710000713869</v>
+        <v>13.94251579623665</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08801454982587592</v>
+        <v>0.0878189735796138</v>
       </c>
       <c r="C21">
-        <v>885.9128192382707</v>
+        <v>879.0457877615528</v>
       </c>
       <c r="D21">
-        <v>1060.907819238271</v>
+        <v>1065.845787761553</v>
       </c>
       <c r="E21">
-        <v>-282.505</v>
+        <v>-270.7</v>
       </c>
       <c r="F21">
-        <v>224.295</v>
+        <v>236.1</v>
       </c>
       <c r="G21">
         <v>49.3</v>
@@ -3009,28 +3009,28 @@
         <v>157.3</v>
       </c>
       <c r="M21">
-        <v>11.2820385</v>
+        <v>11.87583</v>
       </c>
       <c r="N21">
-        <v>146.0179615</v>
+        <v>145.42417</v>
       </c>
       <c r="O21">
-        <v>36.504490375</v>
+        <v>36.3560425</v>
       </c>
       <c r="P21">
-        <v>109.513471125</v>
+        <v>109.0681275</v>
       </c>
       <c r="Q21">
-        <v>154.713471125</v>
+        <v>154.2681275</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09981086398256286</v>
+        <v>0.1003424669745172</v>
       </c>
       <c r="T21">
-        <v>1.082575392743047</v>
+        <v>1.093230662356659</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.94251579623665</v>
+        <v>13.24539000642481</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0878189735796138</v>
+        <v>0.08785964733335164</v>
       </c>
       <c r="C22">
-        <v>879.0457877615528</v>
+        <v>866.2100623075248</v>
       </c>
       <c r="D22">
-        <v>1065.845787761553</v>
+        <v>1064.815062307525</v>
       </c>
       <c r="E22">
-        <v>-270.7</v>
+        <v>-258.895</v>
       </c>
       <c r="F22">
-        <v>236.1</v>
+        <v>247.905</v>
       </c>
       <c r="G22">
         <v>49.3</v>
@@ -3091,45 +3091,45 @@
         <v>157.3</v>
       </c>
       <c r="M22">
-        <v>11.87583</v>
+        <v>12.841479</v>
       </c>
       <c r="N22">
-        <v>145.42417</v>
+        <v>144.458521</v>
       </c>
       <c r="O22">
-        <v>36.3560425</v>
+        <v>36.11463025</v>
       </c>
       <c r="P22">
-        <v>109.0681275</v>
+        <v>108.34389075</v>
       </c>
       <c r="Q22">
-        <v>154.2681275</v>
+        <v>153.54389075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1003424669745172</v>
+        <v>0.1008875282700654</v>
       </c>
       <c r="T22">
-        <v>1.093230662356659</v>
+        <v>1.104155685631376</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.24539000642481</v>
+        <v>12.24936784929524</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08785964733335164</v>
+        <v>0.08767532108708949</v>
       </c>
       <c r="C23">
-        <v>866.2100623075248</v>
+        <v>859.092151464175</v>
       </c>
       <c r="D23">
-        <v>1064.815062307525</v>
+        <v>1069.502151464175</v>
       </c>
       <c r="E23">
-        <v>-258.895</v>
+        <v>-247.09</v>
       </c>
       <c r="F23">
-        <v>247.905</v>
+        <v>259.71</v>
       </c>
       <c r="G23">
         <v>49.3</v>
@@ -3173,28 +3173,28 @@
         <v>157.3</v>
       </c>
       <c r="M23">
-        <v>12.841479</v>
+        <v>13.452978</v>
       </c>
       <c r="N23">
-        <v>144.458521</v>
+        <v>143.847022</v>
       </c>
       <c r="O23">
-        <v>36.11463025</v>
+        <v>35.9617555</v>
       </c>
       <c r="P23">
-        <v>108.34389075</v>
+        <v>107.8852665</v>
       </c>
       <c r="Q23">
-        <v>153.54389075</v>
+        <v>153.0852665</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1008875282700654</v>
+        <v>0.1014465654962686</v>
       </c>
       <c r="T23">
-        <v>1.104155685631376</v>
+        <v>1.115360837708008</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.24936784929524</v>
+        <v>11.6925784016</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08767532108708949</v>
+        <v>0.08749099484082735</v>
       </c>
       <c r="C24">
-        <v>859.092151464175</v>
+        <v>852.0156861921497</v>
       </c>
       <c r="D24">
-        <v>1069.502151464175</v>
+        <v>1074.23068619215</v>
       </c>
       <c r="E24">
-        <v>-247.09</v>
+        <v>-235.285</v>
       </c>
       <c r="F24">
-        <v>259.71</v>
+        <v>271.515</v>
       </c>
       <c r="G24">
         <v>49.3</v>
@@ -3255,28 +3255,28 @@
         <v>157.3</v>
       </c>
       <c r="M24">
-        <v>13.452978</v>
+        <v>14.064477</v>
       </c>
       <c r="N24">
-        <v>143.847022</v>
+        <v>143.235523</v>
       </c>
       <c r="O24">
-        <v>35.9617555</v>
+        <v>35.80888075</v>
       </c>
       <c r="P24">
-        <v>107.8852665</v>
+        <v>107.42664225</v>
       </c>
       <c r="Q24">
-        <v>153.0852665</v>
+        <v>152.62664225</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1014465654962686</v>
+        <v>0.1020201231699056</v>
       </c>
       <c r="T24">
-        <v>1.115360837708008</v>
+        <v>1.126857032695722</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.6925784016</v>
+        <v>11.18420542761739</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08749099484082735</v>
+        <v>0.08730666859456521</v>
       </c>
       <c r="C25">
-        <v>852.0156861921497</v>
+        <v>844.9812186562111</v>
       </c>
       <c r="D25">
-        <v>1074.23068619215</v>
+        <v>1079.001218656211</v>
       </c>
       <c r="E25">
-        <v>-235.285</v>
+        <v>-223.48</v>
       </c>
       <c r="F25">
-        <v>271.515</v>
+        <v>283.3200000000001</v>
       </c>
       <c r="G25">
         <v>49.3</v>
@@ -3337,28 +3337,28 @@
         <v>157.3</v>
       </c>
       <c r="M25">
-        <v>14.064477</v>
+        <v>14.675976</v>
       </c>
       <c r="N25">
-        <v>143.235523</v>
+        <v>142.624024</v>
       </c>
       <c r="O25">
-        <v>35.80888075</v>
+        <v>35.656006</v>
       </c>
       <c r="P25">
-        <v>107.42664225</v>
+        <v>106.968018</v>
       </c>
       <c r="Q25">
-        <v>152.62664225</v>
+        <v>152.168018</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020201231699056</v>
+        <v>0.1026087744665332</v>
       </c>
       <c r="T25">
-        <v>1.126857032695722</v>
+        <v>1.138655759130482</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.18420542761739</v>
+        <v>10.71819686813333</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08730666859456521</v>
+        <v>0.08712234234830306</v>
       </c>
       <c r="C26">
-        <v>844.9812186562112</v>
+        <v>837.9893108732681</v>
       </c>
       <c r="D26">
-        <v>1079.001218656211</v>
+        <v>1083.814310873268</v>
       </c>
       <c r="E26">
-        <v>-223.48</v>
+        <v>-211.675</v>
       </c>
       <c r="F26">
-        <v>283.32</v>
+        <v>295.125</v>
       </c>
       <c r="G26">
         <v>49.3</v>
@@ -3419,28 +3419,28 @@
         <v>157.3</v>
       </c>
       <c r="M26">
-        <v>14.675976</v>
+        <v>15.287475</v>
       </c>
       <c r="N26">
-        <v>142.624024</v>
+        <v>142.012525</v>
       </c>
       <c r="O26">
-        <v>35.656006</v>
+        <v>35.50313125</v>
       </c>
       <c r="P26">
-        <v>106.968018</v>
+        <v>106.50939375</v>
       </c>
       <c r="Q26">
-        <v>152.168018</v>
+        <v>151.70939375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1026087744665332</v>
+        <v>0.1032131231310708</v>
       </c>
       <c r="T26">
-        <v>1.138655759130482</v>
+        <v>1.150769118270168</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.71819686813334</v>
+        <v>10.289468993408</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08712234234830306</v>
+        <v>0.08693801610204092</v>
       </c>
       <c r="C27">
-        <v>837.9893108732681</v>
+        <v>831.0405349330993</v>
       </c>
       <c r="D27">
-        <v>1083.814310873268</v>
+        <v>1088.670534933099</v>
       </c>
       <c r="E27">
-        <v>-211.675</v>
+        <v>-199.87</v>
       </c>
       <c r="F27">
-        <v>295.125</v>
+        <v>306.93</v>
       </c>
       <c r="G27">
         <v>49.3</v>
@@ -3501,28 +3501,28 @@
         <v>157.3</v>
       </c>
       <c r="M27">
-        <v>15.287475</v>
+        <v>15.898974</v>
       </c>
       <c r="N27">
-        <v>142.012525</v>
+        <v>141.401026</v>
       </c>
       <c r="O27">
-        <v>35.50313125</v>
+        <v>35.3502565</v>
       </c>
       <c r="P27">
-        <v>106.50939375</v>
+        <v>106.0507695</v>
       </c>
       <c r="Q27">
-        <v>151.70939375</v>
+        <v>151.2507695</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1032131231310708</v>
+        <v>0.1038338055432985</v>
       </c>
       <c r="T27">
-        <v>1.150769118270168</v>
+        <v>1.16320986549471</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.289468993408</v>
+        <v>9.893720185969233</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08693801610204092</v>
+        <v>0.08709793985577879</v>
       </c>
       <c r="C28">
-        <v>831.0405349330993</v>
+        <v>815.0197246738386</v>
       </c>
       <c r="D28">
-        <v>1088.670534933099</v>
+        <v>1084.454724673839</v>
       </c>
       <c r="E28">
-        <v>-199.87</v>
+        <v>-188.065</v>
       </c>
       <c r="F28">
-        <v>306.93</v>
+        <v>318.735</v>
       </c>
       <c r="G28">
         <v>49.3</v>
@@ -3583,45 +3583,45 @@
         <v>157.3</v>
       </c>
       <c r="M28">
-        <v>15.898974</v>
+        <v>17.0523225</v>
       </c>
       <c r="N28">
-        <v>141.401026</v>
+        <v>140.2476775</v>
       </c>
       <c r="O28">
-        <v>35.3502565</v>
+        <v>35.061919375</v>
       </c>
       <c r="P28">
-        <v>106.0507695</v>
+        <v>105.185758125</v>
       </c>
       <c r="Q28">
-        <v>151.2507695</v>
+        <v>150.385758125</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1038338055432985</v>
+        <v>0.1044714929531216</v>
       </c>
       <c r="T28">
-        <v>1.16320986549471</v>
+        <v>1.175991455108966</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.893720185969233</v>
+        <v>9.224549911016521</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08709793985577879</v>
+        <v>0.08692636360951664</v>
       </c>
       <c r="C29">
-        <v>815.0197246738386</v>
+        <v>807.7389921891349</v>
       </c>
       <c r="D29">
-        <v>1084.454724673839</v>
+        <v>1088.978992189135</v>
       </c>
       <c r="E29">
-        <v>-188.065</v>
+        <v>-176.26</v>
       </c>
       <c r="F29">
-        <v>318.735</v>
+        <v>330.54</v>
       </c>
       <c r="G29">
         <v>49.3</v>
@@ -3665,28 +3665,28 @@
         <v>157.3</v>
       </c>
       <c r="M29">
-        <v>17.0523225</v>
+        <v>17.68389</v>
       </c>
       <c r="N29">
-        <v>140.2476775</v>
+        <v>139.61611</v>
       </c>
       <c r="O29">
-        <v>35.061919375</v>
+        <v>34.90402750000001</v>
       </c>
       <c r="P29">
-        <v>105.185758125</v>
+        <v>104.7120825</v>
       </c>
       <c r="Q29">
-        <v>150.385758125</v>
+        <v>149.9120825</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1044714929531216</v>
+        <v>0.1051268939021064</v>
       </c>
       <c r="T29">
-        <v>1.175991455108966</v>
+        <v>1.189128088879173</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.224549911016521</v>
+        <v>8.895101699908787</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08692636360951664</v>
+        <v>0.0867547873632545</v>
       </c>
       <c r="C30">
-        <v>807.7389921891349</v>
+        <v>800.4961676945504</v>
       </c>
       <c r="D30">
-        <v>1088.978992189135</v>
+        <v>1093.54116769455</v>
       </c>
       <c r="E30">
-        <v>-176.26</v>
+        <v>-164.455</v>
       </c>
       <c r="F30">
-        <v>330.54</v>
+        <v>342.345</v>
       </c>
       <c r="G30">
         <v>49.3</v>
@@ -3747,28 +3747,28 @@
         <v>157.3</v>
       </c>
       <c r="M30">
-        <v>17.68389</v>
+        <v>18.3154575</v>
       </c>
       <c r="N30">
-        <v>139.61611</v>
+        <v>138.9845425</v>
       </c>
       <c r="O30">
-        <v>34.90402750000001</v>
+        <v>34.746135625</v>
       </c>
       <c r="P30">
-        <v>104.7120825</v>
+        <v>104.238406875</v>
       </c>
       <c r="Q30">
-        <v>149.9120825</v>
+        <v>149.438406875</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1051268939021064</v>
+        <v>0.1058007568496542</v>
       </c>
       <c r="T30">
-        <v>1.189128088879173</v>
+        <v>1.202634768671076</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.895101699908787</v>
+        <v>8.588374055084346</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0867547873632545</v>
+        <v>0.08658321111699235</v>
       </c>
       <c r="C31">
-        <v>800.4961676945504</v>
+        <v>793.2917296303903</v>
       </c>
       <c r="D31">
-        <v>1093.54116769455</v>
+        <v>1098.14172963039</v>
       </c>
       <c r="E31">
-        <v>-164.455</v>
+        <v>-152.65</v>
       </c>
       <c r="F31">
-        <v>342.345</v>
+        <v>354.15</v>
       </c>
       <c r="G31">
         <v>49.3</v>
@@ -3829,28 +3829,28 @@
         <v>157.3</v>
       </c>
       <c r="M31">
-        <v>18.3154575</v>
+        <v>18.947025</v>
       </c>
       <c r="N31">
-        <v>138.9845425</v>
+        <v>138.352975</v>
       </c>
       <c r="O31">
-        <v>34.746135625</v>
+        <v>34.58824375</v>
       </c>
       <c r="P31">
-        <v>104.238406875</v>
+        <v>103.76473125</v>
       </c>
       <c r="Q31">
-        <v>149.438406875</v>
+        <v>148.96473125</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1058007568496542</v>
+        <v>0.1064938730242748</v>
       </c>
       <c r="T31">
-        <v>1.202634768671076</v>
+        <v>1.216527353599891</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.588374055084348</v>
+        <v>8.302094919914868</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08658321111699235</v>
+        <v>0.08641163487073021</v>
       </c>
       <c r="C32">
-        <v>793.2917296303903</v>
+        <v>786.1261645222271</v>
       </c>
       <c r="D32">
-        <v>1098.14172963039</v>
+        <v>1102.781164522227</v>
       </c>
       <c r="E32">
-        <v>-152.65</v>
+        <v>-140.845</v>
       </c>
       <c r="F32">
-        <v>354.15</v>
+        <v>365.955</v>
       </c>
       <c r="G32">
         <v>49.3</v>
@@ -3911,28 +3911,28 @@
         <v>157.3</v>
       </c>
       <c r="M32">
-        <v>18.947025</v>
+        <v>19.5785925</v>
       </c>
       <c r="N32">
-        <v>138.352975</v>
+        <v>137.7214075</v>
       </c>
       <c r="O32">
-        <v>34.58824375</v>
+        <v>34.430351875</v>
       </c>
       <c r="P32">
-        <v>103.76473125</v>
+        <v>103.291055625</v>
       </c>
       <c r="Q32">
-        <v>148.96473125</v>
+        <v>148.491055625</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1064938730242748</v>
+        <v>0.1072070795227974</v>
       </c>
       <c r="T32">
-        <v>1.216527353599891</v>
+        <v>1.230822622149831</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.302094919914868</v>
+        <v>8.034285406369227</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08641163487073021</v>
+        <v>0.08624005862446808</v>
       </c>
       <c r="C33">
-        <v>786.1261645222271</v>
+        <v>778.9999671524197</v>
       </c>
       <c r="D33">
-        <v>1102.781164522227</v>
+        <v>1107.45996715242</v>
       </c>
       <c r="E33">
-        <v>-140.845</v>
+        <v>-129.04</v>
       </c>
       <c r="F33">
-        <v>365.955</v>
+        <v>377.76</v>
       </c>
       <c r="G33">
         <v>49.3</v>
@@ -3993,28 +3993,28 @@
         <v>157.3</v>
       </c>
       <c r="M33">
-        <v>19.5785925</v>
+        <v>20.21016</v>
       </c>
       <c r="N33">
-        <v>137.7214075</v>
+        <v>137.08984</v>
       </c>
       <c r="O33">
-        <v>34.430351875</v>
+        <v>34.27246</v>
       </c>
       <c r="P33">
-        <v>103.291055625</v>
+        <v>102.81738</v>
       </c>
       <c r="Q33">
-        <v>148.491055625</v>
+        <v>148.01738</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1072070795227974</v>
+        <v>0.1079412626830413</v>
       </c>
       <c r="T33">
-        <v>1.230822622149831</v>
+        <v>1.24553833977477</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.034285406369227</v>
+        <v>7.78321398742019</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08624005862446808</v>
+        <v>0.08626648237820593</v>
       </c>
       <c r="C34">
-        <v>778.9999671524197</v>
+        <v>766.4718193093956</v>
       </c>
       <c r="D34">
-        <v>1107.45996715242</v>
+        <v>1106.736819309396</v>
       </c>
       <c r="E34">
-        <v>-129.04</v>
+        <v>-117.235</v>
       </c>
       <c r="F34">
-        <v>377.76</v>
+        <v>389.565</v>
       </c>
       <c r="G34">
         <v>49.3</v>
@@ -4075,45 +4075,45 @@
         <v>157.3</v>
       </c>
       <c r="M34">
-        <v>20.21016</v>
+        <v>21.1533795</v>
       </c>
       <c r="N34">
-        <v>137.08984</v>
+        <v>136.1466205</v>
       </c>
       <c r="O34">
-        <v>34.27246</v>
+        <v>34.036655125</v>
       </c>
       <c r="P34">
-        <v>102.81738</v>
+        <v>102.109965375</v>
       </c>
       <c r="Q34">
-        <v>148.01738</v>
+        <v>147.309965375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1079412626830413</v>
+        <v>0.1086973617585163</v>
       </c>
       <c r="T34">
-        <v>1.24553833977477</v>
+        <v>1.260693332552691</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.78321398742019</v>
+        <v>7.436164041778762</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08626648237820593</v>
+        <v>0.08610090613194378</v>
       </c>
       <c r="C35">
-        <v>766.4718193093956</v>
+        <v>759.213846801567</v>
       </c>
       <c r="D35">
-        <v>1106.736819309396</v>
+        <v>1111.283846801567</v>
       </c>
       <c r="E35">
-        <v>-117.235</v>
+        <v>-105.43</v>
       </c>
       <c r="F35">
-        <v>389.565</v>
+        <v>401.37</v>
       </c>
       <c r="G35">
         <v>49.3</v>
@@ -4157,28 +4157,28 @@
         <v>157.3</v>
       </c>
       <c r="M35">
-        <v>21.1533795</v>
+        <v>21.794391</v>
       </c>
       <c r="N35">
-        <v>136.1466205</v>
+        <v>135.505609</v>
       </c>
       <c r="O35">
-        <v>34.036655125</v>
+        <v>33.87640225000001</v>
       </c>
       <c r="P35">
-        <v>102.109965375</v>
+        <v>101.62920675</v>
       </c>
       <c r="Q35">
-        <v>147.309965375</v>
+        <v>146.82920675</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1086973617585163</v>
+        <v>0.1094763729271876</v>
       </c>
       <c r="T35">
-        <v>1.260693332552691</v>
+        <v>1.276307567536004</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.436164041778762</v>
+        <v>7.217453334667622</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08610090613194378</v>
+        <v>0.08593532988568164</v>
       </c>
       <c r="C36">
-        <v>759.213846801567</v>
+        <v>751.9933913514499</v>
       </c>
       <c r="D36">
-        <v>1111.283846801567</v>
+        <v>1115.86839135145</v>
       </c>
       <c r="E36">
-        <v>-105.43</v>
+        <v>-93.625</v>
       </c>
       <c r="F36">
-        <v>401.37</v>
+        <v>413.175</v>
       </c>
       <c r="G36">
         <v>49.3</v>
@@ -4239,28 +4239,28 @@
         <v>157.3</v>
       </c>
       <c r="M36">
-        <v>21.794391</v>
+        <v>22.4354025</v>
       </c>
       <c r="N36">
-        <v>135.505609</v>
+        <v>134.8645975</v>
       </c>
       <c r="O36">
-        <v>33.87640225000001</v>
+        <v>33.716149375</v>
       </c>
       <c r="P36">
-        <v>101.62920675</v>
+        <v>101.148448125</v>
       </c>
       <c r="Q36">
-        <v>146.82920675</v>
+        <v>146.348448125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1094763729271876</v>
+        <v>0.1102793536702795</v>
       </c>
       <c r="T36">
-        <v>1.276307567536004</v>
+        <v>1.292402240518804</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.217453334667622</v>
+        <v>7.011240382248547</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08593532988568164</v>
+        <v>0.08576975363941949</v>
       </c>
       <c r="C37">
-        <v>751.9933913514499</v>
+        <v>744.8109192066213</v>
       </c>
       <c r="D37">
-        <v>1115.86839135145</v>
+        <v>1120.490919206621</v>
       </c>
       <c r="E37">
-        <v>-93.625</v>
+        <v>-81.81999999999994</v>
       </c>
       <c r="F37">
-        <v>413.175</v>
+        <v>424.9800000000001</v>
       </c>
       <c r="G37">
         <v>49.3</v>
@@ -4321,28 +4321,28 @@
         <v>157.3</v>
       </c>
       <c r="M37">
-        <v>22.4354025</v>
+        <v>23.076414</v>
       </c>
       <c r="N37">
-        <v>134.8645975</v>
+        <v>134.223586</v>
       </c>
       <c r="O37">
-        <v>33.716149375</v>
+        <v>33.5558965</v>
       </c>
       <c r="P37">
-        <v>101.148448125</v>
+        <v>100.6676895</v>
       </c>
       <c r="Q37">
-        <v>146.348448125</v>
+        <v>145.8676895</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1102793536702795</v>
+        <v>0.111107427561593</v>
       </c>
       <c r="T37">
-        <v>1.292402240518804</v>
+        <v>1.308999872032315</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.011240382248547</v>
+        <v>6.816483704963865</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08576975363941949</v>
+        <v>0.08560417739315737</v>
       </c>
       <c r="C38">
-        <v>744.8109192066213</v>
+        <v>737.6669043725884</v>
       </c>
       <c r="D38">
-        <v>1120.490919206621</v>
+        <v>1125.151904372588</v>
       </c>
       <c r="E38">
-        <v>-81.82000000000005</v>
+        <v>-70.01500000000004</v>
       </c>
       <c r="F38">
-        <v>424.98</v>
+        <v>436.785</v>
       </c>
       <c r="G38">
         <v>49.3</v>
@@ -4403,28 +4403,28 @@
         <v>157.3</v>
       </c>
       <c r="M38">
-        <v>23.076414</v>
+        <v>23.7174255</v>
       </c>
       <c r="N38">
-        <v>134.223586</v>
+        <v>133.5825745</v>
       </c>
       <c r="O38">
-        <v>33.5558965</v>
+        <v>33.39564362500001</v>
       </c>
       <c r="P38">
-        <v>100.6676895</v>
+        <v>100.186930875</v>
       </c>
       <c r="Q38">
-        <v>145.8676895</v>
+        <v>145.386930875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.111107427561593</v>
+        <v>0.1119617895129482</v>
       </c>
       <c r="T38">
-        <v>1.308999872032315</v>
+        <v>1.326124412482764</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.816483704963866</v>
+        <v>6.632254415640519</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08560417739315737</v>
+        <v>0.08543860114689523</v>
       </c>
       <c r="C39">
-        <v>737.6669043725884</v>
+        <v>730.5618287748222</v>
       </c>
       <c r="D39">
-        <v>1125.151904372588</v>
+        <v>1129.851828774822</v>
       </c>
       <c r="E39">
-        <v>-70.01500000000004</v>
+        <v>-58.20999999999998</v>
       </c>
       <c r="F39">
-        <v>436.785</v>
+        <v>448.59</v>
       </c>
       <c r="G39">
         <v>49.3</v>
@@ -4485,28 +4485,28 @@
         <v>157.3</v>
       </c>
       <c r="M39">
-        <v>23.7174255</v>
+        <v>24.358437</v>
       </c>
       <c r="N39">
-        <v>133.5825745</v>
+        <v>132.941563</v>
       </c>
       <c r="O39">
-        <v>33.39564362500001</v>
+        <v>33.23539075</v>
       </c>
       <c r="P39">
-        <v>100.186930875</v>
+        <v>99.70617225000001</v>
       </c>
       <c r="Q39">
-        <v>145.386930875</v>
+        <v>144.90617225</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1119617895129482</v>
+        <v>0.1128437115272504</v>
       </c>
       <c r="T39">
-        <v>1.326124412482764</v>
+        <v>1.343801357463873</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.632254415640519</v>
+        <v>6.457721404702609</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08543860114689523</v>
+        <v>0.08527302490063308</v>
       </c>
       <c r="C40">
-        <v>730.5618287748222</v>
+        <v>723.4961824248628</v>
       </c>
       <c r="D40">
-        <v>1129.851828774822</v>
+        <v>1134.591182424863</v>
       </c>
       <c r="E40">
-        <v>-58.20999999999998</v>
+        <v>-46.40499999999997</v>
       </c>
       <c r="F40">
-        <v>448.59</v>
+        <v>460.395</v>
       </c>
       <c r="G40">
         <v>49.3</v>
@@ -4567,28 +4567,28 @@
         <v>157.3</v>
       </c>
       <c r="M40">
-        <v>24.358437</v>
+        <v>24.9994485</v>
       </c>
       <c r="N40">
-        <v>132.941563</v>
+        <v>132.3005515</v>
       </c>
       <c r="O40">
-        <v>33.23539075</v>
+        <v>33.075137875</v>
       </c>
       <c r="P40">
-        <v>99.70617225000001</v>
+        <v>99.22541362500002</v>
       </c>
       <c r="Q40">
-        <v>144.90617225</v>
+        <v>144.425413625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1128437115272504</v>
+        <v>0.1137545490174313</v>
       </c>
       <c r="T40">
-        <v>1.343801357463873</v>
+        <v>1.362057874411575</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.457721404702609</v>
+        <v>6.292138804582029</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08527302490063308</v>
+        <v>0.08510744865437095</v>
       </c>
       <c r="C41">
-        <v>723.4961824248628</v>
+        <v>716.4704635906255</v>
       </c>
       <c r="D41">
-        <v>1134.591182424863</v>
+        <v>1139.370463590626</v>
       </c>
       <c r="E41">
-        <v>-46.40499999999997</v>
+        <v>-34.59999999999997</v>
       </c>
       <c r="F41">
-        <v>460.395</v>
+        <v>472.2</v>
       </c>
       <c r="G41">
         <v>49.3</v>
@@ -4649,28 +4649,28 @@
         <v>157.3</v>
       </c>
       <c r="M41">
-        <v>24.9994485</v>
+        <v>25.64046</v>
       </c>
       <c r="N41">
-        <v>132.3005515</v>
+        <v>131.65954</v>
       </c>
       <c r="O41">
-        <v>33.075137875</v>
+        <v>32.914885</v>
       </c>
       <c r="P41">
-        <v>99.22541362500002</v>
+        <v>98.74465499999999</v>
       </c>
       <c r="Q41">
-        <v>144.425413625</v>
+        <v>143.944655</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1137545490174313</v>
+        <v>0.1146957477572849</v>
       </c>
       <c r="T41">
-        <v>1.362057874411575</v>
+        <v>1.380922941924201</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.292138804582029</v>
+        <v>6.134835334467478</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08510744865437095</v>
+        <v>0.0852493724081088</v>
       </c>
       <c r="C42">
-        <v>716.4704635906255</v>
+        <v>700.566444437216</v>
       </c>
       <c r="D42">
-        <v>1139.370463590626</v>
+        <v>1135.271444437216</v>
       </c>
       <c r="E42">
-        <v>-34.59999999999997</v>
+        <v>-22.79499999999996</v>
       </c>
       <c r="F42">
-        <v>472.2</v>
+        <v>484.0050000000001</v>
       </c>
       <c r="G42">
         <v>49.3</v>
@@ -4731,45 +4731,45 @@
         <v>157.3</v>
       </c>
       <c r="M42">
-        <v>25.64046</v>
+        <v>26.76547650000001</v>
       </c>
       <c r="N42">
-        <v>131.65954</v>
+        <v>130.5345235</v>
       </c>
       <c r="O42">
-        <v>32.914885</v>
+        <v>32.633630875</v>
       </c>
       <c r="P42">
-        <v>98.74465499999999</v>
+        <v>97.90089262500001</v>
       </c>
       <c r="Q42">
-        <v>143.944655</v>
+        <v>143.100892625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1146957477572849</v>
+        <v>0.1156688515391675</v>
       </c>
       <c r="T42">
-        <v>1.380922941924201</v>
+        <v>1.400427503250814</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.134835334467478</v>
+        <v>5.876973645509355</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0852493724081088</v>
+        <v>0.08509129616184667</v>
       </c>
       <c r="C43">
-        <v>700.566444437216</v>
+        <v>693.3288541680128</v>
       </c>
       <c r="D43">
-        <v>1135.271444437216</v>
+        <v>1139.838854168013</v>
       </c>
       <c r="E43">
-        <v>-22.79499999999996</v>
+        <v>-10.98999999999995</v>
       </c>
       <c r="F43">
-        <v>484.0050000000001</v>
+        <v>495.8100000000001</v>
       </c>
       <c r="G43">
         <v>49.3</v>
@@ -4813,28 +4813,28 @@
         <v>157.3</v>
       </c>
       <c r="M43">
-        <v>26.76547650000001</v>
+        <v>27.41829300000001</v>
       </c>
       <c r="N43">
-        <v>130.5345235</v>
+        <v>129.881707</v>
       </c>
       <c r="O43">
-        <v>32.633630875</v>
+        <v>32.47042675</v>
       </c>
       <c r="P43">
-        <v>97.90089262500001</v>
+        <v>97.41128025</v>
       </c>
       <c r="Q43">
-        <v>143.100892625</v>
+        <v>142.61128025</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1156688515391675</v>
+        <v>0.1166755106238736</v>
       </c>
       <c r="T43">
-        <v>1.400427503250814</v>
+        <v>1.420604635657655</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.876973645509355</v>
+        <v>5.737045701568657</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08509129616184669</v>
+        <v>0.08493321991558453</v>
       </c>
       <c r="C44">
-        <v>693.3288541680124</v>
+        <v>686.1281634428256</v>
       </c>
       <c r="D44">
-        <v>1139.838854168012</v>
+        <v>1144.443163442826</v>
       </c>
       <c r="E44">
-        <v>-10.99000000000001</v>
+        <v>0.8149999999999977</v>
       </c>
       <c r="F44">
-        <v>495.81</v>
+        <v>507.615</v>
       </c>
       <c r="G44">
         <v>49.3</v>
@@ -4895,28 +4895,28 @@
         <v>157.3</v>
       </c>
       <c r="M44">
-        <v>27.418293</v>
+        <v>28.0711095</v>
       </c>
       <c r="N44">
-        <v>129.881707</v>
+        <v>129.2288905</v>
       </c>
       <c r="O44">
-        <v>32.47042675</v>
+        <v>32.307222625</v>
       </c>
       <c r="P44">
-        <v>97.41128025</v>
+        <v>96.921667875</v>
       </c>
       <c r="Q44">
-        <v>142.61128025</v>
+        <v>142.121667875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1166755106238736</v>
+        <v>0.1177174910799728</v>
       </c>
       <c r="T44">
-        <v>1.420604635657655</v>
+        <v>1.441489737622631</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.737045701568657</v>
+        <v>5.603626034090316</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08493321991558453</v>
+        <v>0.08477514366932239</v>
       </c>
       <c r="C45">
-        <v>686.1281634428256</v>
+        <v>678.9648212356052</v>
       </c>
       <c r="D45">
-        <v>1144.443163442826</v>
+        <v>1149.084821235605</v>
       </c>
       <c r="E45">
-        <v>0.8149999999999977</v>
+        <v>12.61999999999995</v>
       </c>
       <c r="F45">
-        <v>507.615</v>
+        <v>519.42</v>
       </c>
       <c r="G45">
         <v>49.3</v>
@@ -4977,28 +4977,28 @@
         <v>157.3</v>
       </c>
       <c r="M45">
-        <v>28.0711095</v>
+        <v>28.723926</v>
       </c>
       <c r="N45">
-        <v>129.2288905</v>
+        <v>128.576074</v>
       </c>
       <c r="O45">
-        <v>32.307222625</v>
+        <v>32.1440185</v>
       </c>
       <c r="P45">
-        <v>96.921667875</v>
+        <v>96.4320555</v>
       </c>
       <c r="Q45">
-        <v>142.121667875</v>
+        <v>141.6320555</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1177174910799728</v>
+        <v>0.11879668512379</v>
       </c>
       <c r="T45">
-        <v>1.441489737622631</v>
+        <v>1.463120736086356</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.603626034090316</v>
+        <v>5.476270896951901</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08477514366932239</v>
+        <v>0.08461706742306024</v>
       </c>
       <c r="C46">
-        <v>678.9648212356052</v>
+        <v>671.8392838337976</v>
       </c>
       <c r="D46">
-        <v>1149.084821235605</v>
+        <v>1153.764283833798</v>
       </c>
       <c r="E46">
-        <v>12.61999999999995</v>
+        <v>24.42500000000001</v>
       </c>
       <c r="F46">
-        <v>519.42</v>
+        <v>531.225</v>
       </c>
       <c r="G46">
         <v>49.3</v>
@@ -5059,28 +5059,28 @@
         <v>157.3</v>
       </c>
       <c r="M46">
-        <v>28.723926</v>
+        <v>29.3767425</v>
       </c>
       <c r="N46">
-        <v>128.576074</v>
+        <v>127.9232575</v>
       </c>
       <c r="O46">
-        <v>32.1440185</v>
+        <v>31.980814375</v>
       </c>
       <c r="P46">
-        <v>96.4320555</v>
+        <v>95.94244312500001</v>
       </c>
       <c r="Q46">
-        <v>141.6320555</v>
+        <v>141.142443125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.11879668512379</v>
+        <v>0.1199151225873822</v>
       </c>
       <c r="T46">
-        <v>1.463120736086356</v>
+        <v>1.485538316312398</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.476270896951901</v>
+        <v>5.354575988130747</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08461706742306024</v>
+        <v>0.0844589911767981</v>
       </c>
       <c r="C47">
-        <v>671.8392838337976</v>
+        <v>664.7520149878699</v>
       </c>
       <c r="D47">
-        <v>1153.764283833798</v>
+        <v>1158.48201498787</v>
       </c>
       <c r="E47">
-        <v>24.42500000000001</v>
+        <v>36.22999999999996</v>
       </c>
       <c r="F47">
-        <v>531.225</v>
+        <v>543.03</v>
       </c>
       <c r="G47">
         <v>49.3</v>
@@ -5141,28 +5141,28 @@
         <v>157.3</v>
       </c>
       <c r="M47">
-        <v>29.3767425</v>
+        <v>30.029559</v>
       </c>
       <c r="N47">
-        <v>127.9232575</v>
+        <v>127.270441</v>
       </c>
       <c r="O47">
-        <v>31.980814375</v>
+        <v>31.81761025</v>
       </c>
       <c r="P47">
-        <v>95.94244312500001</v>
+        <v>95.45283075</v>
       </c>
       <c r="Q47">
-        <v>141.142443125</v>
+        <v>140.65283075</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1199151225873822</v>
+        <v>0.1210749836607372</v>
       </c>
       <c r="T47">
-        <v>1.485538316312398</v>
+        <v>1.508786177287553</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.354575988130747</v>
+        <v>5.238172162301818</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0844589911767981</v>
+        <v>0.08430091493053596</v>
       </c>
       <c r="C48">
-        <v>664.7520149878699</v>
+        <v>657.7034860645153</v>
       </c>
       <c r="D48">
-        <v>1158.48201498787</v>
+        <v>1163.238486064515</v>
       </c>
       <c r="E48">
-        <v>36.22999999999996</v>
+        <v>48.03500000000003</v>
       </c>
       <c r="F48">
-        <v>543.03</v>
+        <v>554.835</v>
       </c>
       <c r="G48">
         <v>49.3</v>
@@ -5223,28 +5223,28 @@
         <v>157.3</v>
       </c>
       <c r="M48">
-        <v>30.029559</v>
+        <v>30.6823755</v>
       </c>
       <c r="N48">
-        <v>127.270441</v>
+        <v>126.6176245</v>
       </c>
       <c r="O48">
-        <v>31.81761025</v>
+        <v>31.654406125</v>
       </c>
       <c r="P48">
-        <v>95.45283075</v>
+        <v>94.963218375</v>
       </c>
       <c r="Q48">
-        <v>140.65283075</v>
+        <v>140.163218375</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1210749836607372</v>
+        <v>0.1222786130764829</v>
       </c>
       <c r="T48">
-        <v>1.508786177287553</v>
+        <v>1.532911316035355</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.238172162301818</v>
+        <v>5.126721690763481</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08430091493053596</v>
+        <v>0.0841428386842738</v>
       </c>
       <c r="C49">
-        <v>657.7034860645153</v>
+        <v>650.6941762036538</v>
       </c>
       <c r="D49">
-        <v>1163.238486064515</v>
+        <v>1168.034176203654</v>
       </c>
       <c r="E49">
-        <v>48.03500000000003</v>
+        <v>59.84000000000009</v>
       </c>
       <c r="F49">
-        <v>554.835</v>
+        <v>566.6400000000001</v>
       </c>
       <c r="G49">
         <v>49.3</v>
@@ -5305,28 +5305,28 @@
         <v>157.3</v>
       </c>
       <c r="M49">
-        <v>30.6823755</v>
+        <v>31.33519200000001</v>
       </c>
       <c r="N49">
-        <v>126.6176245</v>
+        <v>125.964808</v>
       </c>
       <c r="O49">
-        <v>31.654406125</v>
+        <v>31.491202</v>
       </c>
       <c r="P49">
-        <v>94.963218375</v>
+        <v>94.473606</v>
       </c>
       <c r="Q49">
-        <v>140.163218375</v>
+        <v>139.673606</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1222786130764829</v>
+        <v>0.1235285359312958</v>
       </c>
       <c r="T49">
-        <v>1.532911316035355</v>
+        <v>1.557964344734996</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.126721690763481</v>
+        <v>5.019914988872574</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0841428386842738</v>
+        <v>0.08398476243801167</v>
       </c>
       <c r="C50">
-        <v>650.6941762036539</v>
+        <v>643.7245724793252</v>
       </c>
       <c r="D50">
-        <v>1168.034176203654</v>
+        <v>1172.869572479325</v>
       </c>
       <c r="E50">
-        <v>59.83999999999997</v>
+        <v>71.64499999999992</v>
       </c>
       <c r="F50">
-        <v>566.64</v>
+        <v>578.4449999999999</v>
       </c>
       <c r="G50">
         <v>49.3</v>
@@ -5387,28 +5387,28 @@
         <v>157.3</v>
       </c>
       <c r="M50">
-        <v>31.335192</v>
+        <v>31.9880085</v>
       </c>
       <c r="N50">
-        <v>125.964808</v>
+        <v>125.3119915</v>
       </c>
       <c r="O50">
-        <v>31.491202</v>
+        <v>31.327997875</v>
       </c>
       <c r="P50">
-        <v>94.473606</v>
+        <v>93.98399362500001</v>
       </c>
       <c r="Q50">
-        <v>139.673606</v>
+        <v>139.183993625</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1235285359312958</v>
+        <v>0.1248274753686503</v>
       </c>
       <c r="T50">
-        <v>1.557964344734996</v>
+        <v>1.583999845148348</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.019914988872575</v>
+        <v>4.917467744201707</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08398476243801167</v>
+        <v>0.08382668619174954</v>
       </c>
       <c r="C51">
-        <v>643.7245724793252</v>
+        <v>636.7951700646026</v>
       </c>
       <c r="D51">
-        <v>1172.869572479325</v>
+        <v>1177.745170064603</v>
       </c>
       <c r="E51">
-        <v>71.64499999999992</v>
+        <v>83.44999999999999</v>
       </c>
       <c r="F51">
-        <v>578.4449999999999</v>
+        <v>590.25</v>
       </c>
       <c r="G51">
         <v>49.3</v>
@@ -5469,28 +5469,28 @@
         <v>157.3</v>
       </c>
       <c r="M51">
-        <v>31.9880085</v>
+        <v>32.640825</v>
       </c>
       <c r="N51">
-        <v>125.3119915</v>
+        <v>124.659175</v>
       </c>
       <c r="O51">
-        <v>31.327997875</v>
+        <v>31.16479375</v>
       </c>
       <c r="P51">
-        <v>93.98399362500001</v>
+        <v>93.49438125</v>
       </c>
       <c r="Q51">
-        <v>139.183993625</v>
+        <v>138.69438125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1248274753686503</v>
+        <v>0.1261783723834991</v>
       </c>
       <c r="T51">
-        <v>1.583999845148348</v>
+        <v>1.611076765578235</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.917467744201707</v>
+        <v>4.819118389317673</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08382668619174954</v>
+        <v>0.08366860994548739</v>
       </c>
       <c r="C52">
-        <v>636.7951700646026</v>
+        <v>629.9064724006323</v>
       </c>
       <c r="D52">
-        <v>1177.745170064603</v>
+        <v>1182.661472400632</v>
       </c>
       <c r="E52">
-        <v>83.44999999999999</v>
+        <v>95.25500000000005</v>
       </c>
       <c r="F52">
-        <v>590.25</v>
+        <v>602.0550000000001</v>
       </c>
       <c r="G52">
         <v>49.3</v>
@@ -5551,28 +5551,28 @@
         <v>157.3</v>
       </c>
       <c r="M52">
-        <v>32.640825</v>
+        <v>33.29364150000001</v>
       </c>
       <c r="N52">
-        <v>124.659175</v>
+        <v>124.0063585</v>
       </c>
       <c r="O52">
-        <v>31.16479375</v>
+        <v>31.001589625</v>
       </c>
       <c r="P52">
-        <v>93.49438125</v>
+        <v>93.004768875</v>
       </c>
       <c r="Q52">
-        <v>138.69438125</v>
+        <v>138.204768875</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1261783723834991</v>
+        <v>0.1275844080520151</v>
       </c>
       <c r="T52">
-        <v>1.611076765578235</v>
+        <v>1.639258866433831</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.819118389317673</v>
+        <v>4.72462587188007</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08366860994548739</v>
+        <v>0.08351053369922525</v>
       </c>
       <c r="C53">
-        <v>629.9064724006323</v>
+        <v>623.0589913699222</v>
       </c>
       <c r="D53">
-        <v>1182.661472400632</v>
+        <v>1187.618991369922</v>
       </c>
       <c r="E53">
-        <v>95.25500000000005</v>
+        <v>107.06</v>
       </c>
       <c r="F53">
-        <v>602.0550000000001</v>
+        <v>613.86</v>
       </c>
       <c r="G53">
         <v>49.3</v>
@@ -5633,28 +5633,28 @@
         <v>157.3</v>
       </c>
       <c r="M53">
-        <v>33.29364150000001</v>
+        <v>33.946458</v>
       </c>
       <c r="N53">
-        <v>124.0063585</v>
+        <v>123.353542</v>
       </c>
       <c r="O53">
-        <v>31.001589625</v>
+        <v>30.8383855</v>
       </c>
       <c r="P53">
-        <v>93.004768875</v>
+        <v>92.5151565</v>
       </c>
       <c r="Q53">
-        <v>138.204768875</v>
+        <v>137.7151565</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1275844080520151</v>
+        <v>0.1290490285400526</v>
       </c>
       <c r="T53">
-        <v>1.639258866433831</v>
+        <v>1.668615221491743</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.72462587188007</v>
+        <v>4.633767682036224</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08351053369922525</v>
+        <v>0.0833524574529631</v>
       </c>
       <c r="C54">
-        <v>623.0589913699222</v>
+        <v>616.2532474740141</v>
       </c>
       <c r="D54">
-        <v>1187.618991369922</v>
+        <v>1192.618247474014</v>
       </c>
       <c r="E54">
-        <v>107.06</v>
+        <v>118.8650000000001</v>
       </c>
       <c r="F54">
-        <v>613.86</v>
+        <v>625.6650000000001</v>
       </c>
       <c r="G54">
         <v>49.3</v>
@@ -5715,28 +5715,28 @@
         <v>157.3</v>
       </c>
       <c r="M54">
-        <v>33.946458</v>
+        <v>34.59927450000001</v>
       </c>
       <c r="N54">
-        <v>123.353542</v>
+        <v>122.7007255</v>
       </c>
       <c r="O54">
-        <v>30.8383855</v>
+        <v>30.675181375</v>
       </c>
       <c r="P54">
-        <v>92.5151565</v>
+        <v>92.02554412500001</v>
       </c>
       <c r="Q54">
-        <v>137.7151565</v>
+        <v>137.225544125</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1290490285400526</v>
+        <v>0.1305759733041768</v>
       </c>
       <c r="T54">
-        <v>1.668615221491743</v>
+        <v>1.699220783147865</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.633767682036224</v>
+        <v>4.546338103129878</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0833524574529631</v>
+        <v>0.08420688120670096</v>
       </c>
       <c r="C55">
-        <v>616.2532474740141</v>
+        <v>577.9165081667045</v>
       </c>
       <c r="D55">
-        <v>1192.618247474014</v>
+        <v>1166.086508166705</v>
       </c>
       <c r="E55">
-        <v>118.8650000000001</v>
+        <v>130.67</v>
       </c>
       <c r="F55">
-        <v>625.6650000000001</v>
+        <v>637.47</v>
       </c>
       <c r="G55">
         <v>49.3</v>
@@ -5797,45 +5797,45 @@
         <v>157.3</v>
       </c>
       <c r="M55">
-        <v>34.59927450000001</v>
+        <v>36.845766</v>
       </c>
       <c r="N55">
-        <v>122.7007255</v>
+        <v>120.454234</v>
       </c>
       <c r="O55">
-        <v>30.675181375</v>
+        <v>30.1135585</v>
       </c>
       <c r="P55">
-        <v>92.02554412500001</v>
+        <v>90.3406755</v>
       </c>
       <c r="Q55">
-        <v>137.225544125</v>
+        <v>135.5406755</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1305759733041768</v>
+        <v>0.1321693069710891</v>
       </c>
       <c r="T55">
-        <v>1.699220783147865</v>
+        <v>1.73115702139773</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.546338103129878</v>
+        <v>4.269147233904704</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08420688120670096</v>
+        <v>0.08406755496043883</v>
       </c>
       <c r="C56">
-        <v>577.9165081667045</v>
+        <v>570.3570487079733</v>
       </c>
       <c r="D56">
-        <v>1166.086508166705</v>
+        <v>1170.332048707973</v>
       </c>
       <c r="E56">
-        <v>130.67</v>
+        <v>142.4750000000001</v>
       </c>
       <c r="F56">
-        <v>637.47</v>
+        <v>649.2750000000001</v>
       </c>
       <c r="G56">
         <v>49.3</v>
@@ -5879,28 +5879,28 @@
         <v>157.3</v>
       </c>
       <c r="M56">
-        <v>36.845766</v>
+        <v>37.52809500000001</v>
       </c>
       <c r="N56">
-        <v>120.454234</v>
+        <v>119.771905</v>
       </c>
       <c r="O56">
-        <v>30.1135585</v>
+        <v>29.94297625</v>
       </c>
       <c r="P56">
-        <v>90.3406755</v>
+        <v>89.82892875</v>
       </c>
       <c r="Q56">
-        <v>135.5406755</v>
+        <v>135.02892875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1321693069710891</v>
+        <v>0.1338334554676419</v>
       </c>
       <c r="T56">
-        <v>1.73115702139773</v>
+        <v>1.764512648014257</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.269147233904704</v>
+        <v>4.191526375106436</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08406755496043883</v>
+        <v>0.08392822871417668</v>
       </c>
       <c r="C57">
-        <v>570.3570487079733</v>
+        <v>562.8286169285722</v>
       </c>
       <c r="D57">
-        <v>1170.332048707973</v>
+        <v>1174.608616928572</v>
       </c>
       <c r="E57">
-        <v>142.4750000000001</v>
+        <v>154.28</v>
       </c>
       <c r="F57">
-        <v>649.2750000000001</v>
+        <v>661.08</v>
       </c>
       <c r="G57">
         <v>49.3</v>
@@ -5961,28 +5961,28 @@
         <v>157.3</v>
       </c>
       <c r="M57">
-        <v>37.52809500000001</v>
+        <v>38.210424</v>
       </c>
       <c r="N57">
-        <v>119.771905</v>
+        <v>119.089576</v>
       </c>
       <c r="O57">
-        <v>29.94297625</v>
+        <v>29.772394</v>
       </c>
       <c r="P57">
-        <v>89.82892875</v>
+        <v>89.317182</v>
       </c>
       <c r="Q57">
-        <v>135.02892875</v>
+        <v>134.517182</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1338334554676419</v>
+        <v>0.1355732470776743</v>
       </c>
       <c r="T57">
-        <v>1.764512648014257</v>
+        <v>1.799384439476989</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.191526375106436</v>
+        <v>4.116677689836679</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08392822871417668</v>
+        <v>0.08378890246791454</v>
       </c>
       <c r="C58">
-        <v>562.8286169285722</v>
+        <v>555.3315542153113</v>
       </c>
       <c r="D58">
-        <v>1174.608616928572</v>
+        <v>1178.916554215311</v>
       </c>
       <c r="E58">
-        <v>154.28</v>
+        <v>166.0850000000001</v>
       </c>
       <c r="F58">
-        <v>661.08</v>
+        <v>672.8850000000001</v>
       </c>
       <c r="G58">
         <v>49.3</v>
@@ -6043,28 +6043,28 @@
         <v>157.3</v>
       </c>
       <c r="M58">
-        <v>38.210424</v>
+        <v>38.89275300000001</v>
       </c>
       <c r="N58">
-        <v>119.089576</v>
+        <v>118.407247</v>
       </c>
       <c r="O58">
-        <v>29.772394</v>
+        <v>29.60181175</v>
       </c>
       <c r="P58">
-        <v>89.317182</v>
+        <v>88.80543525000002</v>
       </c>
       <c r="Q58">
-        <v>134.517182</v>
+        <v>134.00543525</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1355732470776743</v>
+        <v>0.1373939592277083</v>
       </c>
       <c r="T58">
-        <v>1.799384439476989</v>
+        <v>1.835878174728686</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.116677689836679</v>
+        <v>4.044455274225509</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08378890246791454</v>
+        <v>0.0851720762216524</v>
       </c>
       <c r="C59">
-        <v>555.3315542153113</v>
+        <v>502.1102360496732</v>
       </c>
       <c r="D59">
-        <v>1178.916554215311</v>
+        <v>1137.500236049673</v>
       </c>
       <c r="E59">
-        <v>166.0850000000001</v>
+        <v>177.89</v>
       </c>
       <c r="F59">
-        <v>672.8850000000001</v>
+        <v>684.6900000000001</v>
       </c>
       <c r="G59">
         <v>49.3</v>
@@ -6125,45 +6125,45 @@
         <v>157.3</v>
       </c>
       <c r="M59">
-        <v>38.89275300000001</v>
+        <v>41.97149700000001</v>
       </c>
       <c r="N59">
-        <v>118.407247</v>
+        <v>115.328503</v>
       </c>
       <c r="O59">
-        <v>29.60181175</v>
+        <v>28.83212575</v>
       </c>
       <c r="P59">
-        <v>88.80543525000002</v>
+        <v>86.49637725000001</v>
       </c>
       <c r="Q59">
-        <v>134.00543525</v>
+        <v>131.69637725</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1373939592277083</v>
+        <v>0.1393013719563153</v>
       </c>
       <c r="T59">
-        <v>1.835878174728686</v>
+        <v>1.87410970689713</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.044455274225509</v>
+        <v>3.747781500383462</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0851720762216524</v>
+        <v>0.08505899997539026</v>
       </c>
       <c r="C60">
-        <v>502.1102360496733</v>
+        <v>493.5815359272918</v>
       </c>
       <c r="D60">
-        <v>1137.500236049673</v>
+        <v>1140.776535927292</v>
       </c>
       <c r="E60">
-        <v>177.8899999999999</v>
+        <v>189.695</v>
       </c>
       <c r="F60">
-        <v>684.6899999999999</v>
+        <v>696.495</v>
       </c>
       <c r="G60">
         <v>49.3</v>
@@ -6207,28 +6207,28 @@
         <v>157.3</v>
       </c>
       <c r="M60">
-        <v>41.971497</v>
+        <v>42.6951435</v>
       </c>
       <c r="N60">
-        <v>115.328503</v>
+        <v>114.6048565</v>
       </c>
       <c r="O60">
-        <v>28.83212575</v>
+        <v>28.651214125</v>
       </c>
       <c r="P60">
-        <v>86.49637725000001</v>
+        <v>85.95364237500002</v>
       </c>
       <c r="Q60">
-        <v>131.69637725</v>
+        <v>131.153642375</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1393013719563152</v>
+        <v>0.1413018292082689</v>
       </c>
       <c r="T60">
-        <v>1.87410970689713</v>
+        <v>1.914206191854279</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.747781500383463</v>
+        <v>3.68425978003798</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08505899997539026</v>
+        <v>0.08494592372912811</v>
       </c>
       <c r="C61">
-        <v>493.5815359272918</v>
+        <v>485.0717635325768</v>
       </c>
       <c r="D61">
-        <v>1140.776535927292</v>
+        <v>1144.071763532577</v>
       </c>
       <c r="E61">
-        <v>189.695</v>
+        <v>201.4999999999999</v>
       </c>
       <c r="F61">
-        <v>696.495</v>
+        <v>708.3</v>
       </c>
       <c r="G61">
         <v>49.3</v>
@@ -6289,28 +6289,28 @@
         <v>157.3</v>
       </c>
       <c r="M61">
-        <v>42.6951435</v>
+        <v>43.41878999999999</v>
       </c>
       <c r="N61">
-        <v>114.6048565</v>
+        <v>113.88121</v>
       </c>
       <c r="O61">
-        <v>28.651214125</v>
+        <v>28.4703025</v>
       </c>
       <c r="P61">
-        <v>85.95364237500002</v>
+        <v>85.41090750000001</v>
       </c>
       <c r="Q61">
-        <v>131.153642375</v>
+        <v>130.6109075</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1413018292082689</v>
+        <v>0.1434023093228203</v>
       </c>
       <c r="T61">
-        <v>1.914206191854279</v>
+        <v>1.956307501059285</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.68425978003798</v>
+        <v>3.622855450370681</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08494592372912811</v>
+        <v>0.08483284748286599</v>
       </c>
       <c r="C62">
-        <v>485.0717635325768</v>
+        <v>476.5810833636253</v>
       </c>
       <c r="D62">
-        <v>1144.071763532577</v>
+        <v>1147.386083363625</v>
       </c>
       <c r="E62">
-        <v>201.4999999999999</v>
+        <v>213.305</v>
       </c>
       <c r="F62">
-        <v>708.3</v>
+        <v>720.105</v>
       </c>
       <c r="G62">
         <v>49.3</v>
@@ -6371,28 +6371,28 @@
         <v>157.3</v>
       </c>
       <c r="M62">
-        <v>43.41878999999999</v>
+        <v>44.1424365</v>
       </c>
       <c r="N62">
-        <v>113.88121</v>
+        <v>113.1575635</v>
       </c>
       <c r="O62">
-        <v>28.4703025</v>
+        <v>28.289390875</v>
       </c>
       <c r="P62">
-        <v>85.41090750000001</v>
+        <v>84.868172625</v>
       </c>
       <c r="Q62">
-        <v>130.6109075</v>
+        <v>130.068172625</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1434023093228203</v>
+        <v>0.145610506366323</v>
       </c>
       <c r="T62">
-        <v>1.956307501059285</v>
+        <v>2.000567851761984</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.622855450370681</v>
+        <v>3.563464377413784</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08483284748286599</v>
+        <v>0.08471977123660385</v>
       </c>
       <c r="C63">
-        <v>476.5810833636253</v>
+        <v>468.1096618302469</v>
       </c>
       <c r="D63">
-        <v>1147.386083363625</v>
+        <v>1150.719661830247</v>
       </c>
       <c r="E63">
-        <v>213.305</v>
+        <v>225.11</v>
       </c>
       <c r="F63">
-        <v>720.105</v>
+        <v>731.91</v>
       </c>
       <c r="G63">
         <v>49.3</v>
@@ -6453,28 +6453,28 @@
         <v>157.3</v>
       </c>
       <c r="M63">
-        <v>44.1424365</v>
+        <v>44.866083</v>
       </c>
       <c r="N63">
-        <v>113.1575635</v>
+        <v>112.433917</v>
       </c>
       <c r="O63">
-        <v>28.289390875</v>
+        <v>28.10847925</v>
       </c>
       <c r="P63">
-        <v>84.868172625</v>
+        <v>84.32543775000001</v>
       </c>
       <c r="Q63">
-        <v>130.068172625</v>
+        <v>129.52543775</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.145610506366323</v>
+        <v>0.1479349243068522</v>
       </c>
       <c r="T63">
-        <v>2.000567851761984</v>
+        <v>2.04715769460693</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.563464377413784</v>
+        <v>3.505989145520014</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08471977123660385</v>
+        <v>0.0859296949903417</v>
       </c>
       <c r="C64">
-        <v>468.1096618302469</v>
+        <v>421.6100783534299</v>
       </c>
       <c r="D64">
-        <v>1150.719661830247</v>
+        <v>1116.02507835343</v>
       </c>
       <c r="E64">
-        <v>225.11</v>
+        <v>236.915</v>
       </c>
       <c r="F64">
-        <v>731.91</v>
+        <v>743.715</v>
       </c>
       <c r="G64">
         <v>49.3</v>
@@ -6535,45 +6535,45 @@
         <v>157.3</v>
       </c>
       <c r="M64">
-        <v>44.866083</v>
+        <v>47.67213150000001</v>
       </c>
       <c r="N64">
-        <v>112.433917</v>
+        <v>109.6278685</v>
       </c>
       <c r="O64">
-        <v>28.10847925</v>
+        <v>27.406967125</v>
       </c>
       <c r="P64">
-        <v>84.32543775000001</v>
+        <v>82.22090137500001</v>
       </c>
       <c r="Q64">
-        <v>129.52543775</v>
+        <v>127.420901375</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1479349243068522</v>
+        <v>0.150384986460383</v>
       </c>
       <c r="T64">
-        <v>2.04715769460693</v>
+        <v>2.096265907335386</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.505989145520014</v>
+        <v>3.299621708754516</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0859296949903417</v>
+        <v>0.08583761874407955</v>
       </c>
       <c r="C65">
-        <v>421.6100783534299</v>
+        <v>412.3716495725139</v>
       </c>
       <c r="D65">
-        <v>1116.02507835343</v>
+        <v>1118.591649572514</v>
       </c>
       <c r="E65">
-        <v>236.915</v>
+        <v>248.72</v>
       </c>
       <c r="F65">
-        <v>743.715</v>
+        <v>755.52</v>
       </c>
       <c r="G65">
         <v>49.3</v>
@@ -6617,28 +6617,28 @@
         <v>157.3</v>
       </c>
       <c r="M65">
-        <v>47.67213150000001</v>
+        <v>48.428832</v>
       </c>
       <c r="N65">
-        <v>109.6278685</v>
+        <v>108.871168</v>
       </c>
       <c r="O65">
-        <v>27.406967125</v>
+        <v>27.217792</v>
       </c>
       <c r="P65">
-        <v>82.22090137500001</v>
+        <v>81.65337600000001</v>
       </c>
       <c r="Q65">
-        <v>127.420901375</v>
+        <v>126.853376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.150384986460383</v>
+        <v>0.1529711631779987</v>
       </c>
       <c r="T65">
-        <v>2.096265907335386</v>
+        <v>2.148102354104313</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.299621708754516</v>
+        <v>3.248065119555227</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08583761874407955</v>
+        <v>0.08574554249781742</v>
       </c>
       <c r="C66">
-        <v>412.3716495725139</v>
+        <v>403.1450529124716</v>
       </c>
       <c r="D66">
-        <v>1118.591649572514</v>
+        <v>1121.170052912472</v>
       </c>
       <c r="E66">
-        <v>248.72</v>
+        <v>260.525</v>
       </c>
       <c r="F66">
-        <v>755.52</v>
+        <v>767.325</v>
       </c>
       <c r="G66">
         <v>49.3</v>
@@ -6699,28 +6699,28 @@
         <v>157.3</v>
       </c>
       <c r="M66">
-        <v>48.428832</v>
+        <v>49.18553250000001</v>
       </c>
       <c r="N66">
-        <v>108.871168</v>
+        <v>108.1144675</v>
       </c>
       <c r="O66">
-        <v>27.217792</v>
+        <v>27.028616875</v>
       </c>
       <c r="P66">
-        <v>81.65337600000001</v>
+        <v>81.08585062500001</v>
       </c>
       <c r="Q66">
-        <v>126.853376</v>
+        <v>126.285850625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1529711631779987</v>
+        <v>0.1557051214223355</v>
       </c>
       <c r="T66">
-        <v>2.148102354104313</v>
+        <v>2.20290088354575</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.248065119555227</v>
+        <v>3.198094886946685</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08574554249781742</v>
+        <v>0.08565346625155529</v>
       </c>
       <c r="C67">
-        <v>403.1450529124716</v>
+        <v>393.9303703830295</v>
       </c>
       <c r="D67">
-        <v>1121.170052912472</v>
+        <v>1123.76037038303</v>
       </c>
       <c r="E67">
-        <v>260.525</v>
+        <v>272.33</v>
       </c>
       <c r="F67">
-        <v>767.325</v>
+        <v>779.13</v>
       </c>
       <c r="G67">
         <v>49.3</v>
@@ -6781,28 +6781,28 @@
         <v>157.3</v>
       </c>
       <c r="M67">
-        <v>49.18553250000001</v>
+        <v>49.942233</v>
       </c>
       <c r="N67">
-        <v>108.1144675</v>
+        <v>107.357767</v>
       </c>
       <c r="O67">
-        <v>27.028616875</v>
+        <v>26.83944175</v>
       </c>
       <c r="P67">
-        <v>81.08585062500001</v>
+        <v>80.51832525</v>
       </c>
       <c r="Q67">
-        <v>126.285850625</v>
+        <v>125.71832525</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1557051214223355</v>
+        <v>0.1585999007398685</v>
       </c>
       <c r="T67">
-        <v>2.20290088354575</v>
+        <v>2.260922855895506</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.198094886946685</v>
+        <v>3.149638903811129</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08565346625155529</v>
+        <v>0.08556139000529313</v>
       </c>
       <c r="C68">
-        <v>393.9303703830295</v>
+        <v>384.7276847535601</v>
       </c>
       <c r="D68">
-        <v>1123.76037038303</v>
+        <v>1126.36268475356</v>
       </c>
       <c r="E68">
-        <v>272.33</v>
+        <v>284.135</v>
       </c>
       <c r="F68">
-        <v>779.13</v>
+        <v>790.9350000000001</v>
       </c>
       <c r="G68">
         <v>49.3</v>
@@ -6863,28 +6863,28 @@
         <v>157.3</v>
       </c>
       <c r="M68">
-        <v>49.942233</v>
+        <v>50.69893350000001</v>
       </c>
       <c r="N68">
-        <v>107.357767</v>
+        <v>106.6010665</v>
       </c>
       <c r="O68">
-        <v>26.83944175</v>
+        <v>26.650266625</v>
       </c>
       <c r="P68">
-        <v>80.51832525</v>
+        <v>79.950799875</v>
       </c>
       <c r="Q68">
-        <v>125.71832525</v>
+        <v>125.150799875</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1585999007398685</v>
+        <v>0.161670121228161</v>
       </c>
       <c r="T68">
-        <v>2.260922855895506</v>
+        <v>2.322461311417975</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.149638903811129</v>
+        <v>3.102629367933351</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08556139000529313</v>
+        <v>0.08546931375903098</v>
       </c>
       <c r="C69">
-        <v>384.7276847535601</v>
+        <v>375.537079561896</v>
       </c>
       <c r="D69">
-        <v>1126.36268475356</v>
+        <v>1128.977079561896</v>
       </c>
       <c r="E69">
-        <v>284.135</v>
+        <v>295.94</v>
       </c>
       <c r="F69">
-        <v>790.9350000000001</v>
+        <v>802.74</v>
       </c>
       <c r="G69">
         <v>49.3</v>
@@ -6945,28 +6945,28 @@
         <v>157.3</v>
       </c>
       <c r="M69">
-        <v>50.69893350000001</v>
+        <v>51.455634</v>
       </c>
       <c r="N69">
-        <v>106.6010665</v>
+        <v>105.844366</v>
       </c>
       <c r="O69">
-        <v>26.650266625</v>
+        <v>26.4610915</v>
       </c>
       <c r="P69">
-        <v>79.950799875</v>
+        <v>79.3832745</v>
       </c>
       <c r="Q69">
-        <v>125.150799875</v>
+        <v>124.5832745</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.161670121228161</v>
+        <v>0.1649322304969718</v>
       </c>
       <c r="T69">
-        <v>2.322461311417975</v>
+        <v>2.387845920410598</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.102629367933351</v>
+        <v>3.057002465463743</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08546931375903098</v>
+        <v>0.08537723751276885</v>
       </c>
       <c r="C70">
-        <v>375.537079561896</v>
+        <v>366.358639123273</v>
       </c>
       <c r="D70">
-        <v>1128.977079561896</v>
+        <v>1131.603639123273</v>
       </c>
       <c r="E70">
-        <v>295.94</v>
+        <v>307.7450000000001</v>
       </c>
       <c r="F70">
-        <v>802.74</v>
+        <v>814.5450000000001</v>
       </c>
       <c r="G70">
         <v>49.3</v>
@@ -7027,28 +7027,28 @@
         <v>157.3</v>
       </c>
       <c r="M70">
-        <v>51.455634</v>
+        <v>52.21233450000001</v>
       </c>
       <c r="N70">
-        <v>105.844366</v>
+        <v>105.0876655</v>
       </c>
       <c r="O70">
-        <v>26.4610915</v>
+        <v>26.271916375</v>
       </c>
       <c r="P70">
-        <v>79.3832745</v>
+        <v>78.815749125</v>
       </c>
       <c r="Q70">
-        <v>124.5832745</v>
+        <v>124.015749125</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1649322304969718</v>
+        <v>0.1684047984282866</v>
       </c>
       <c r="T70">
-        <v>2.387845920410598</v>
+        <v>2.457448891273713</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.057002465463743</v>
+        <v>3.012698081906297</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08537723751276885</v>
+        <v>0.08938016126650669</v>
       </c>
       <c r="C71">
-        <v>366.358639123273</v>
+        <v>250.6136133128583</v>
       </c>
       <c r="D71">
-        <v>1131.603639123273</v>
+        <v>1027.663613312858</v>
       </c>
       <c r="E71">
-        <v>307.7450000000001</v>
+        <v>319.55</v>
       </c>
       <c r="F71">
-        <v>814.5450000000001</v>
+        <v>826.35</v>
       </c>
       <c r="G71">
         <v>49.3</v>
@@ -7109,45 +7109,45 @@
         <v>157.3</v>
       </c>
       <c r="M71">
-        <v>52.21233450000001</v>
+        <v>59.414565</v>
       </c>
       <c r="N71">
-        <v>105.0876655</v>
+        <v>97.885435</v>
       </c>
       <c r="O71">
-        <v>26.271916375</v>
+        <v>24.47135875</v>
       </c>
       <c r="P71">
-        <v>78.815749125</v>
+        <v>73.41407624999999</v>
       </c>
       <c r="Q71">
-        <v>124.015749125</v>
+        <v>118.61407625</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1684047984282866</v>
+        <v>0.1721088708883557</v>
       </c>
       <c r="T71">
-        <v>2.457448891273713</v>
+        <v>2.531692060194369</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.012698081906297</v>
+        <v>2.647498976050738</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08938016126650669</v>
+        <v>0.08934658502024456</v>
       </c>
       <c r="C72">
-        <v>250.6136133128583</v>
+        <v>239.6009851266109</v>
       </c>
       <c r="D72">
-        <v>1027.663613312858</v>
+        <v>1028.455985126611</v>
       </c>
       <c r="E72">
-        <v>319.55</v>
+        <v>331.3550000000001</v>
       </c>
       <c r="F72">
-        <v>826.35</v>
+        <v>838.1550000000001</v>
       </c>
       <c r="G72">
         <v>49.3</v>
@@ -7191,28 +7191,28 @@
         <v>157.3</v>
       </c>
       <c r="M72">
-        <v>59.414565</v>
+        <v>60.26334450000001</v>
       </c>
       <c r="N72">
-        <v>97.885435</v>
+        <v>97.03665549999999</v>
       </c>
       <c r="O72">
-        <v>24.47135875</v>
+        <v>24.259163875</v>
       </c>
       <c r="P72">
-        <v>73.41407624999999</v>
+        <v>72.777491625</v>
       </c>
       <c r="Q72">
-        <v>118.61407625</v>
+        <v>117.977491625</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1721088708883557</v>
+        <v>0.176068396621533</v>
       </c>
       <c r="T72">
-        <v>2.531692060194369</v>
+        <v>2.611055447661277</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.647498976050738</v>
+        <v>2.610210258078192</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08934658502024456</v>
+        <v>0.08931300877398242</v>
       </c>
       <c r="C73">
-        <v>239.600985126611</v>
+        <v>228.5895797871357</v>
       </c>
       <c r="D73">
-        <v>1028.455985126611</v>
+        <v>1029.249579787136</v>
       </c>
       <c r="E73">
-        <v>331.355</v>
+        <v>343.1599999999999</v>
       </c>
       <c r="F73">
-        <v>838.155</v>
+        <v>849.9599999999999</v>
       </c>
       <c r="G73">
         <v>49.3</v>
@@ -7273,28 +7273,28 @@
         <v>157.3</v>
       </c>
       <c r="M73">
-        <v>60.2633445</v>
+        <v>61.112124</v>
       </c>
       <c r="N73">
-        <v>97.03665550000001</v>
+        <v>96.18787600000002</v>
       </c>
       <c r="O73">
-        <v>24.259163875</v>
+        <v>24.046969</v>
       </c>
       <c r="P73">
-        <v>72.77749162500001</v>
+        <v>72.14090700000001</v>
       </c>
       <c r="Q73">
-        <v>117.977491625</v>
+        <v>117.340907</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.176068396621533</v>
+        <v>0.1803107456213658</v>
       </c>
       <c r="T73">
-        <v>2.611055447661277</v>
+        <v>2.696087648518678</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.610210258078192</v>
+        <v>2.573957337827106</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08931300877398242</v>
+        <v>0.08927943252772028</v>
       </c>
       <c r="C74">
-        <v>228.5895797871357</v>
+        <v>217.5794001273988</v>
       </c>
       <c r="D74">
-        <v>1029.249579787136</v>
+        <v>1030.044400127399</v>
       </c>
       <c r="E74">
-        <v>343.1599999999999</v>
+        <v>354.965</v>
       </c>
       <c r="F74">
-        <v>849.9599999999999</v>
+        <v>861.765</v>
       </c>
       <c r="G74">
         <v>49.3</v>
@@ -7355,28 +7355,28 @@
         <v>157.3</v>
       </c>
       <c r="M74">
-        <v>61.112124</v>
+        <v>61.9609035</v>
       </c>
       <c r="N74">
-        <v>96.18787600000002</v>
+        <v>95.33909650000001</v>
       </c>
       <c r="O74">
-        <v>24.046969</v>
+        <v>23.834774125</v>
       </c>
       <c r="P74">
-        <v>72.14090700000001</v>
+        <v>71.50432237500002</v>
       </c>
       <c r="Q74">
-        <v>117.340907</v>
+        <v>116.704322375</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1803107456213658</v>
+        <v>0.1848673426952603</v>
       </c>
       <c r="T74">
-        <v>2.696087648518678</v>
+        <v>2.787418530921072</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.573957337827106</v>
+        <v>2.538697648267831</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08927943252772028</v>
+        <v>0.08924585628145813</v>
       </c>
       <c r="C75">
-        <v>217.5794001273988</v>
+        <v>206.5704489891261</v>
       </c>
       <c r="D75">
-        <v>1030.044400127399</v>
+        <v>1030.840448989126</v>
       </c>
       <c r="E75">
-        <v>354.965</v>
+        <v>366.7699999999999</v>
       </c>
       <c r="F75">
-        <v>861.765</v>
+        <v>873.5699999999999</v>
       </c>
       <c r="G75">
         <v>49.3</v>
@@ -7437,28 +7437,28 @@
         <v>157.3</v>
       </c>
       <c r="M75">
-        <v>61.9609035</v>
+        <v>62.809683</v>
       </c>
       <c r="N75">
-        <v>95.33909650000001</v>
+        <v>94.490317</v>
       </c>
       <c r="O75">
-        <v>23.834774125</v>
+        <v>23.62257925</v>
       </c>
       <c r="P75">
-        <v>71.50432237500002</v>
+        <v>70.86773775</v>
       </c>
       <c r="Q75">
-        <v>116.704322375</v>
+        <v>116.06773775</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1848673426952603</v>
+        <v>0.1897744472363774</v>
       </c>
       <c r="T75">
-        <v>2.787418530921072</v>
+        <v>2.885774865815958</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.538697648267831</v>
+        <v>2.504390923291238</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08924585628145813</v>
+        <v>0.091406030035196</v>
       </c>
       <c r="C76">
-        <v>206.5704489891261</v>
+        <v>145.9386933938865</v>
       </c>
       <c r="D76">
-        <v>1030.840448989126</v>
+        <v>982.0136933938865</v>
       </c>
       <c r="E76">
-        <v>366.7699999999999</v>
+        <v>378.575</v>
       </c>
       <c r="F76">
-        <v>873.5699999999999</v>
+        <v>885.375</v>
       </c>
       <c r="G76">
         <v>49.3</v>
@@ -7519,45 +7519,45 @@
         <v>157.3</v>
       </c>
       <c r="M76">
-        <v>62.809683</v>
+        <v>67.11142500000001</v>
       </c>
       <c r="N76">
-        <v>94.490317</v>
+        <v>90.188575</v>
       </c>
       <c r="O76">
-        <v>23.62257925</v>
+        <v>22.54714375</v>
       </c>
       <c r="P76">
-        <v>70.86773775</v>
+        <v>67.64143125</v>
       </c>
       <c r="Q76">
-        <v>116.06773775</v>
+        <v>112.84143125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1897744472363774</v>
+        <v>0.195074120140784</v>
       </c>
       <c r="T76">
-        <v>2.885774865815958</v>
+        <v>2.991999707502436</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.504390923291238</v>
+        <v>2.343863209580187</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.091406030035196</v>
+        <v>0.09140170378893385</v>
       </c>
       <c r="C77">
-        <v>145.9386933938865</v>
+        <v>134.2268573048248</v>
       </c>
       <c r="D77">
-        <v>982.0136933938865</v>
+        <v>982.1068573048249</v>
       </c>
       <c r="E77">
-        <v>378.575</v>
+        <v>390.3800000000001</v>
       </c>
       <c r="F77">
-        <v>885.375</v>
+        <v>897.1800000000001</v>
       </c>
       <c r="G77">
         <v>49.3</v>
@@ -7601,28 +7601,28 @@
         <v>157.3</v>
       </c>
       <c r="M77">
-        <v>67.11142500000001</v>
+        <v>68.00624400000001</v>
       </c>
       <c r="N77">
-        <v>90.188575</v>
+        <v>89.293756</v>
       </c>
       <c r="O77">
-        <v>22.54714375</v>
+        <v>22.323439</v>
       </c>
       <c r="P77">
-        <v>67.64143125</v>
+        <v>66.97031699999999</v>
       </c>
       <c r="Q77">
-        <v>112.84143125</v>
+        <v>112.170317</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.195074120140784</v>
+        <v>0.2008154324538911</v>
       </c>
       <c r="T77">
-        <v>2.991999707502436</v>
+        <v>3.107076619329452</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.343863209580187</v>
+        <v>2.313022904190974</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09140170378893385</v>
+        <v>0.09139737754267171</v>
       </c>
       <c r="C78">
-        <v>134.2268573048248</v>
+        <v>122.515038894412</v>
       </c>
       <c r="D78">
-        <v>982.1068573048249</v>
+        <v>982.2000388944119</v>
       </c>
       <c r="E78">
-        <v>390.3800000000001</v>
+        <v>402.185</v>
       </c>
       <c r="F78">
-        <v>897.1800000000001</v>
+        <v>908.985</v>
       </c>
       <c r="G78">
         <v>49.3</v>
@@ -7683,28 +7683,28 @@
         <v>157.3</v>
       </c>
       <c r="M78">
-        <v>68.00624400000001</v>
+        <v>68.90106300000001</v>
       </c>
       <c r="N78">
-        <v>89.293756</v>
+        <v>88.398937</v>
       </c>
       <c r="O78">
-        <v>22.323439</v>
+        <v>22.09973425</v>
       </c>
       <c r="P78">
-        <v>66.97031699999999</v>
+        <v>66.29920275000001</v>
       </c>
       <c r="Q78">
-        <v>112.170317</v>
+        <v>111.49920275</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2008154324538911</v>
+        <v>0.207055989315964</v>
       </c>
       <c r="T78">
-        <v>3.107076619329452</v>
+        <v>3.232160219141427</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.313022904190974</v>
+        <v>2.282983645694987</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09139737754267171</v>
+        <v>0.09139305129640957</v>
       </c>
       <c r="C79">
-        <v>122.515038894412</v>
+        <v>110.8032381676811</v>
       </c>
       <c r="D79">
-        <v>982.2000388944119</v>
+        <v>982.2932381676811</v>
       </c>
       <c r="E79">
-        <v>402.185</v>
+        <v>413.9900000000001</v>
       </c>
       <c r="F79">
-        <v>908.985</v>
+        <v>920.7900000000001</v>
       </c>
       <c r="G79">
         <v>49.3</v>
@@ -7765,28 +7765,28 @@
         <v>157.3</v>
       </c>
       <c r="M79">
-        <v>68.90106300000001</v>
+        <v>69.79588200000001</v>
       </c>
       <c r="N79">
-        <v>88.398937</v>
+        <v>87.50411800000001</v>
       </c>
       <c r="O79">
-        <v>22.09973425</v>
+        <v>21.8760295</v>
       </c>
       <c r="P79">
-        <v>66.29920275000001</v>
+        <v>65.6280885</v>
       </c>
       <c r="Q79">
-        <v>111.49920275</v>
+        <v>110.8280885</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.207055989315964</v>
+        <v>0.2138638695291344</v>
       </c>
       <c r="T79">
-        <v>3.232160219141427</v>
+        <v>3.368615055299945</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.282983645694987</v>
+        <v>2.253714624596333</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09139305129640957</v>
+        <v>0.09138872505014743</v>
       </c>
       <c r="C80">
-        <v>110.8032381676811</v>
+        <v>99.0914551296662</v>
       </c>
       <c r="D80">
-        <v>982.2932381676811</v>
+        <v>982.3864551296662</v>
       </c>
       <c r="E80">
-        <v>413.9900000000001</v>
+        <v>425.795</v>
       </c>
       <c r="F80">
-        <v>920.7900000000001</v>
+        <v>932.595</v>
       </c>
       <c r="G80">
         <v>49.3</v>
@@ -7847,28 +7847,28 @@
         <v>157.3</v>
       </c>
       <c r="M80">
-        <v>69.79588200000001</v>
+        <v>70.690701</v>
       </c>
       <c r="N80">
-        <v>87.50411800000001</v>
+        <v>86.60929900000001</v>
       </c>
       <c r="O80">
-        <v>21.8760295</v>
+        <v>21.65232475</v>
       </c>
       <c r="P80">
-        <v>65.6280885</v>
+        <v>64.95697425</v>
       </c>
       <c r="Q80">
-        <v>110.8280885</v>
+        <v>110.15697425</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2138638695291344</v>
+        <v>0.2213201192864163</v>
       </c>
       <c r="T80">
-        <v>3.368615055299945</v>
+        <v>3.518065590140227</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.253714624596333</v>
+        <v>2.225186591373595</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09138872505014743</v>
+        <v>0.0913843988038853</v>
       </c>
       <c r="C81">
-        <v>99.0914551296662</v>
+        <v>87.37968978540334</v>
       </c>
       <c r="D81">
-        <v>982.3864551296662</v>
+        <v>982.4796897854035</v>
       </c>
       <c r="E81">
-        <v>425.795</v>
+        <v>437.6000000000001</v>
       </c>
       <c r="F81">
-        <v>932.595</v>
+        <v>944.4000000000001</v>
       </c>
       <c r="G81">
         <v>49.3</v>
@@ -7929,28 +7929,28 @@
         <v>157.3</v>
       </c>
       <c r="M81">
-        <v>70.690701</v>
+        <v>71.58552000000002</v>
       </c>
       <c r="N81">
-        <v>86.60929900000001</v>
+        <v>85.71447999999999</v>
       </c>
       <c r="O81">
-        <v>21.65232475</v>
+        <v>21.42862</v>
       </c>
       <c r="P81">
-        <v>64.95697425</v>
+        <v>64.28586</v>
       </c>
       <c r="Q81">
-        <v>110.15697425</v>
+        <v>109.48586</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2213201192864163</v>
+        <v>0.2295219940194265</v>
       </c>
       <c r="T81">
-        <v>3.518065590140227</v>
+        <v>3.682461178464537</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.225186591373595</v>
+        <v>2.197371758981425</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0913843988038853</v>
+        <v>0.09138007255762315</v>
       </c>
       <c r="C82">
-        <v>87.37968978540334</v>
+        <v>75.66794213993182</v>
       </c>
       <c r="D82">
-        <v>982.4796897854035</v>
+        <v>982.5729421399318</v>
       </c>
       <c r="E82">
-        <v>437.6000000000001</v>
+        <v>449.405</v>
       </c>
       <c r="F82">
-        <v>944.4000000000001</v>
+        <v>956.205</v>
       </c>
       <c r="G82">
         <v>49.3</v>
@@ -8011,28 +8011,28 @@
         <v>157.3</v>
       </c>
       <c r="M82">
-        <v>71.58552000000002</v>
+        <v>72.48033900000001</v>
       </c>
       <c r="N82">
-        <v>85.71447999999999</v>
+        <v>84.819661</v>
       </c>
       <c r="O82">
-        <v>21.42862</v>
+        <v>21.20491525</v>
       </c>
       <c r="P82">
-        <v>64.28586</v>
+        <v>63.61474575</v>
       </c>
       <c r="Q82">
-        <v>109.48586</v>
+        <v>108.81474575</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2295219940194265</v>
+        <v>0.2385872239874903</v>
       </c>
       <c r="T82">
-        <v>3.682461178464537</v>
+        <v>3.864161565559827</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.197371758981425</v>
+        <v>2.170243712574247</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09138007255762315</v>
+        <v>0.091375746311361</v>
       </c>
       <c r="C83">
-        <v>75.66794213993182</v>
+        <v>63.95621219829093</v>
       </c>
       <c r="D83">
-        <v>982.5729421399318</v>
+        <v>982.666212198291</v>
       </c>
       <c r="E83">
-        <v>449.405</v>
+        <v>461.2100000000001</v>
       </c>
       <c r="F83">
-        <v>956.205</v>
+        <v>968.0100000000001</v>
       </c>
       <c r="G83">
         <v>49.3</v>
@@ -8093,28 +8093,28 @@
         <v>157.3</v>
       </c>
       <c r="M83">
-        <v>72.48033900000001</v>
+        <v>73.37515800000001</v>
       </c>
       <c r="N83">
-        <v>84.819661</v>
+        <v>83.924842</v>
       </c>
       <c r="O83">
-        <v>21.20491525</v>
+        <v>20.9812105</v>
       </c>
       <c r="P83">
-        <v>63.61474575</v>
+        <v>62.9436315</v>
       </c>
       <c r="Q83">
-        <v>108.81474575</v>
+        <v>108.1436315</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2385872239874903</v>
+        <v>0.2486597017297834</v>
       </c>
       <c r="T83">
-        <v>3.864161565559827</v>
+        <v>4.066050884554593</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.170243712574247</v>
+        <v>2.143777325835536</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.091375746311361</v>
+        <v>0.09137142006509885</v>
       </c>
       <c r="C84">
-        <v>63.95621219829093</v>
+        <v>52.24449996552289</v>
       </c>
       <c r="D84">
-        <v>982.666212198291</v>
+        <v>982.7594999655229</v>
       </c>
       <c r="E84">
-        <v>461.2100000000001</v>
+        <v>473.015</v>
       </c>
       <c r="F84">
-        <v>968.0100000000001</v>
+        <v>979.8150000000001</v>
       </c>
       <c r="G84">
         <v>49.3</v>
@@ -8175,28 +8175,28 @@
         <v>157.3</v>
       </c>
       <c r="M84">
-        <v>73.37515800000001</v>
+        <v>74.26997700000001</v>
       </c>
       <c r="N84">
-        <v>83.924842</v>
+        <v>83.030023</v>
       </c>
       <c r="O84">
-        <v>20.9812105</v>
+        <v>20.75750575</v>
       </c>
       <c r="P84">
-        <v>62.9436315</v>
+        <v>62.27251725</v>
       </c>
       <c r="Q84">
-        <v>108.1436315</v>
+        <v>107.47251725</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2486597017297834</v>
+        <v>0.2599171768535228</v>
       </c>
       <c r="T84">
-        <v>4.066050884554593</v>
+        <v>4.291691888136979</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.143777325835536</v>
+        <v>2.117948683355591</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09137142006509885</v>
+        <v>0.09136709381883673</v>
       </c>
       <c r="C85">
-        <v>52.24449996552289</v>
+        <v>40.53280544667086</v>
       </c>
       <c r="D85">
-        <v>982.7594999655229</v>
+        <v>982.852805446671</v>
       </c>
       <c r="E85">
-        <v>473.015</v>
+        <v>484.8200000000001</v>
       </c>
       <c r="F85">
-        <v>979.8150000000001</v>
+        <v>991.6200000000001</v>
       </c>
       <c r="G85">
         <v>49.3</v>
@@ -8257,28 +8257,28 @@
         <v>157.3</v>
       </c>
       <c r="M85">
-        <v>74.26997700000001</v>
+        <v>75.16479600000001</v>
       </c>
       <c r="N85">
-        <v>83.030023</v>
+        <v>82.135204</v>
       </c>
       <c r="O85">
-        <v>20.75750575</v>
+        <v>20.533801</v>
       </c>
       <c r="P85">
-        <v>62.27251725</v>
+        <v>61.601403</v>
       </c>
       <c r="Q85">
-        <v>107.47251725</v>
+        <v>106.801403</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2599171768535228</v>
+        <v>0.2725818363677296</v>
       </c>
       <c r="T85">
-        <v>4.291691888136979</v>
+        <v>4.545538017167164</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.117948683355591</v>
+        <v>2.092735008553738</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09136709381883673</v>
+        <v>0.09136276757257458</v>
       </c>
       <c r="C86">
-        <v>40.53280544667098</v>
+        <v>28.82112864678265</v>
       </c>
       <c r="D86">
-        <v>982.852805446671</v>
+        <v>982.9461286467825</v>
       </c>
       <c r="E86">
-        <v>484.82</v>
+        <v>496.6249999999999</v>
       </c>
       <c r="F86">
-        <v>991.62</v>
+        <v>1003.425</v>
       </c>
       <c r="G86">
         <v>49.3</v>
@@ -8339,28 +8339,28 @@
         <v>157.3</v>
       </c>
       <c r="M86">
-        <v>75.16479600000001</v>
+        <v>76.05961500000001</v>
       </c>
       <c r="N86">
-        <v>82.135204</v>
+        <v>81.240385</v>
       </c>
       <c r="O86">
-        <v>20.533801</v>
+        <v>20.31009625</v>
       </c>
       <c r="P86">
-        <v>61.601403</v>
+        <v>60.93028875</v>
       </c>
       <c r="Q86">
-        <v>106.801403</v>
+        <v>106.13028875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2725818363677294</v>
+        <v>0.2869351171504972</v>
       </c>
       <c r="T86">
-        <v>4.545538017167161</v>
+        <v>4.833230296734704</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.092735008553738</v>
+        <v>2.0681145966884</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09136276757257458</v>
+        <v>0.09135844132631243</v>
       </c>
       <c r="C87">
-        <v>28.82112864678265</v>
+        <v>17.10946957090437</v>
       </c>
       <c r="D87">
-        <v>982.9461286467825</v>
+        <v>983.0394695709043</v>
       </c>
       <c r="E87">
-        <v>496.6249999999999</v>
+        <v>508.43</v>
       </c>
       <c r="F87">
-        <v>1003.425</v>
+        <v>1015.23</v>
       </c>
       <c r="G87">
         <v>49.3</v>
@@ -8421,28 +8421,28 @@
         <v>157.3</v>
       </c>
       <c r="M87">
-        <v>76.05961500000001</v>
+        <v>76.95443400000001</v>
       </c>
       <c r="N87">
-        <v>81.240385</v>
+        <v>80.34556600000001</v>
       </c>
       <c r="O87">
-        <v>20.31009625</v>
+        <v>20.0863915</v>
       </c>
       <c r="P87">
-        <v>60.93028875</v>
+        <v>60.2591745</v>
       </c>
       <c r="Q87">
-        <v>106.13028875</v>
+        <v>105.4591745</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2869351171504972</v>
+        <v>0.3033388666165174</v>
       </c>
       <c r="T87">
-        <v>4.833230296734704</v>
+        <v>5.162021473383322</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.0681145966884</v>
+        <v>2.044066752540861</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09135844132631243</v>
+        <v>0.0913541150800503</v>
       </c>
       <c r="C88">
-        <v>17.10946957090437</v>
+        <v>5.39782822408597</v>
       </c>
       <c r="D88">
-        <v>983.0394695709043</v>
+        <v>983.1328282240861</v>
       </c>
       <c r="E88">
-        <v>508.43</v>
+        <v>520.2350000000001</v>
       </c>
       <c r="F88">
-        <v>1015.23</v>
+        <v>1027.035</v>
       </c>
       <c r="G88">
         <v>49.3</v>
@@ -8503,28 +8503,28 @@
         <v>157.3</v>
       </c>
       <c r="M88">
-        <v>76.95443400000001</v>
+        <v>77.84925300000002</v>
       </c>
       <c r="N88">
-        <v>80.34556600000001</v>
+        <v>79.45074699999999</v>
       </c>
       <c r="O88">
-        <v>20.0863915</v>
+        <v>19.86268675</v>
       </c>
       <c r="P88">
-        <v>60.2591745</v>
+        <v>59.58806025</v>
       </c>
       <c r="Q88">
-        <v>105.4591745</v>
+        <v>104.78806025</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3033388666165174</v>
+        <v>0.3222662698465407</v>
       </c>
       <c r="T88">
-        <v>5.162021473383322</v>
+        <v>5.541395907977883</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.044066752540861</v>
+        <v>2.020571732396713</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0913541150800503</v>
+        <v>0.1007217888337882</v>
       </c>
       <c r="C89">
-        <v>5.39782822408597</v>
+        <v>-174.094127844741</v>
       </c>
       <c r="D89">
-        <v>983.1328282240861</v>
+        <v>815.4458721552589</v>
       </c>
       <c r="E89">
-        <v>520.2350000000001</v>
+        <v>532.04</v>
       </c>
       <c r="F89">
-        <v>1027.035</v>
+        <v>1038.84</v>
       </c>
       <c r="G89">
         <v>49.3</v>
@@ -8585,45 +8585,45 @@
         <v>157.3</v>
       </c>
       <c r="M89">
-        <v>77.84925300000002</v>
+        <v>93.4956</v>
       </c>
       <c r="N89">
-        <v>79.45074699999999</v>
+        <v>63.80440000000002</v>
       </c>
       <c r="O89">
-        <v>19.86268675</v>
+        <v>15.9511</v>
       </c>
       <c r="P89">
-        <v>59.58806025</v>
+        <v>47.85330000000001</v>
       </c>
       <c r="Q89">
-        <v>104.78806025</v>
+        <v>93.05330000000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3222662698465407</v>
+        <v>0.344348240281568</v>
       </c>
       <c r="T89">
-        <v>5.541395907977883</v>
+        <v>5.983999415004871</v>
       </c>
       <c r="U89">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.020571732396713</v>
+        <v>1.682432114452445</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1007217888337882</v>
+        <v>0.100823962587526</v>
       </c>
       <c r="C90">
-        <v>-174.094127844741</v>
+        <v>-187.4133256925536</v>
       </c>
       <c r="D90">
-        <v>815.4458721552589</v>
+        <v>813.9316743074464</v>
       </c>
       <c r="E90">
-        <v>532.04</v>
+        <v>543.845</v>
       </c>
       <c r="F90">
-        <v>1038.84</v>
+        <v>1050.645</v>
       </c>
       <c r="G90">
         <v>49.3</v>
@@ -8667,28 +8667,28 @@
         <v>157.3</v>
       </c>
       <c r="M90">
-        <v>93.4956</v>
+        <v>94.55804999999999</v>
       </c>
       <c r="N90">
-        <v>63.80440000000002</v>
+        <v>62.74195000000002</v>
       </c>
       <c r="O90">
-        <v>15.9511</v>
+        <v>15.6854875</v>
       </c>
       <c r="P90">
-        <v>47.85330000000001</v>
+        <v>47.05646250000001</v>
       </c>
       <c r="Q90">
-        <v>93.05330000000001</v>
+        <v>92.25646250000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.344348240281568</v>
+        <v>0.3704451144320546</v>
       </c>
       <c r="T90">
-        <v>5.983999415004871</v>
+        <v>6.507076286945856</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.682432114452445</v>
+        <v>1.663528382829384</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.100823962587526</v>
+        <v>0.1009261363412639</v>
       </c>
       <c r="C91">
-        <v>-187.4133256925536</v>
+        <v>-200.7269105484794</v>
       </c>
       <c r="D91">
-        <v>813.9316743074464</v>
+        <v>812.4230894515207</v>
       </c>
       <c r="E91">
-        <v>543.845</v>
+        <v>555.6500000000001</v>
       </c>
       <c r="F91">
-        <v>1050.645</v>
+        <v>1062.45</v>
       </c>
       <c r="G91">
         <v>49.3</v>
@@ -8749,28 +8749,28 @@
         <v>157.3</v>
       </c>
       <c r="M91">
-        <v>94.55804999999999</v>
+        <v>95.62050000000001</v>
       </c>
       <c r="N91">
-        <v>62.74195000000002</v>
+        <v>61.6795</v>
       </c>
       <c r="O91">
-        <v>15.6854875</v>
+        <v>15.419875</v>
       </c>
       <c r="P91">
-        <v>47.05646250000001</v>
+        <v>46.259625</v>
       </c>
       <c r="Q91">
-        <v>92.25646250000001</v>
+        <v>91.459625</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3704451144320546</v>
+        <v>0.4017613634126388</v>
       </c>
       <c r="T91">
-        <v>6.507076286945856</v>
+        <v>7.13476853327504</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.663528382829384</v>
+        <v>1.645044734131279</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1009261363412639</v>
+        <v>0.1010283100950017</v>
       </c>
       <c r="C92">
-        <v>-200.7269105484794</v>
+        <v>-214.0349135650446</v>
       </c>
       <c r="D92">
-        <v>812.4230894515207</v>
+        <v>810.9200864349556</v>
       </c>
       <c r="E92">
-        <v>555.6500000000001</v>
+        <v>567.4550000000002</v>
       </c>
       <c r="F92">
-        <v>1062.45</v>
+        <v>1074.255</v>
       </c>
       <c r="G92">
         <v>49.3</v>
@@ -8831,28 +8831,28 @@
         <v>157.3</v>
       </c>
       <c r="M92">
-        <v>95.62050000000001</v>
+        <v>96.68295000000001</v>
       </c>
       <c r="N92">
-        <v>61.6795</v>
+        <v>60.61705000000001</v>
       </c>
       <c r="O92">
-        <v>15.419875</v>
+        <v>15.1542625</v>
       </c>
       <c r="P92">
-        <v>46.259625</v>
+        <v>45.4627875</v>
       </c>
       <c r="Q92">
-        <v>91.459625</v>
+        <v>90.66278750000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4017613634126388</v>
+        <v>0.4400367788333526</v>
       </c>
       <c r="T92">
-        <v>7.13476853327504</v>
+        <v>7.901947945455152</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.645044734131279</v>
+        <v>1.626967319470496</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1010283100950017</v>
+        <v>0.1011304838487396</v>
       </c>
       <c r="C93">
-        <v>-214.0349135650446</v>
+        <v>-227.337365664668</v>
       </c>
       <c r="D93">
-        <v>810.9200864349556</v>
+        <v>809.422634335332</v>
       </c>
       <c r="E93">
-        <v>567.4550000000002</v>
+        <v>579.26</v>
       </c>
       <c r="F93">
-        <v>1074.255</v>
+        <v>1086.06</v>
       </c>
       <c r="G93">
         <v>49.3</v>
@@ -8913,28 +8913,28 @@
         <v>157.3</v>
       </c>
       <c r="M93">
-        <v>96.68295000000001</v>
+        <v>97.74539999999999</v>
       </c>
       <c r="N93">
-        <v>60.61705000000001</v>
+        <v>59.55460000000002</v>
       </c>
       <c r="O93">
-        <v>15.1542625</v>
+        <v>14.88865000000001</v>
       </c>
       <c r="P93">
-        <v>45.4627875</v>
+        <v>44.66595000000002</v>
       </c>
       <c r="Q93">
-        <v>90.66278750000001</v>
+        <v>89.86595000000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4400367788333526</v>
+        <v>0.4878810481092451</v>
       </c>
       <c r="T93">
-        <v>7.901947945455152</v>
+        <v>8.860922210680295</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.626967319470496</v>
+        <v>1.609282892084948</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1011304838487396</v>
+        <v>0.1012326576024775</v>
       </c>
       <c r="C94">
-        <v>-227.337365664668</v>
+        <v>-240.6342975417847</v>
       </c>
       <c r="D94">
-        <v>809.422634335332</v>
+        <v>807.9307024582154</v>
       </c>
       <c r="E94">
-        <v>579.26</v>
+        <v>591.0650000000001</v>
       </c>
       <c r="F94">
-        <v>1086.06</v>
+        <v>1097.865</v>
       </c>
       <c r="G94">
         <v>49.3</v>
@@ -8995,28 +8995,28 @@
         <v>157.3</v>
       </c>
       <c r="M94">
-        <v>97.74539999999999</v>
+        <v>98.80785</v>
       </c>
       <c r="N94">
-        <v>59.55460000000002</v>
+        <v>58.49215000000001</v>
       </c>
       <c r="O94">
-        <v>14.88865000000001</v>
+        <v>14.6230375</v>
       </c>
       <c r="P94">
-        <v>44.66595000000002</v>
+        <v>43.86911250000001</v>
       </c>
       <c r="Q94">
-        <v>89.86595000000003</v>
+        <v>89.06911250000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4878810481092451</v>
+        <v>0.5493951086068209</v>
       </c>
       <c r="T94">
-        <v>8.860922210680295</v>
+        <v>10.09388912311262</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.609282892084948</v>
+        <v>1.591978774965754</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1012326576024775</v>
+        <v>0.1013348313562153</v>
       </c>
       <c r="C95">
-        <v>-240.6342975417847</v>
+        <v>-253.92573966494</v>
       </c>
       <c r="D95">
-        <v>807.9307024582154</v>
+        <v>806.4442603350601</v>
       </c>
       <c r="E95">
-        <v>591.0650000000001</v>
+        <v>602.8700000000001</v>
       </c>
       <c r="F95">
-        <v>1097.865</v>
+        <v>1109.67</v>
       </c>
       <c r="G95">
         <v>49.3</v>
@@ -9077,28 +9077,28 @@
         <v>157.3</v>
       </c>
       <c r="M95">
-        <v>98.80785</v>
+        <v>99.8703</v>
       </c>
       <c r="N95">
-        <v>58.49215000000001</v>
+        <v>57.42970000000001</v>
       </c>
       <c r="O95">
-        <v>14.6230375</v>
+        <v>14.357425</v>
       </c>
       <c r="P95">
-        <v>43.86911250000001</v>
+        <v>43.072275</v>
       </c>
       <c r="Q95">
-        <v>89.06911250000002</v>
+        <v>88.27227500000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5493951086068209</v>
+        <v>0.6314138559369221</v>
       </c>
       <c r="T95">
-        <v>10.09388912311262</v>
+        <v>11.73784500635572</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.591978774965754</v>
+        <v>1.575042830551225</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1013348313562153</v>
+        <v>0.1014370051099532</v>
       </c>
       <c r="C96">
-        <v>-253.92573966494</v>
+        <v>-267.2117222788671</v>
       </c>
       <c r="D96">
-        <v>806.4442603350601</v>
+        <v>804.9632777211331</v>
       </c>
       <c r="E96">
-        <v>602.8700000000001</v>
+        <v>614.6750000000002</v>
       </c>
       <c r="F96">
-        <v>1109.67</v>
+        <v>1121.475</v>
       </c>
       <c r="G96">
         <v>49.3</v>
@@ -9159,28 +9159,28 @@
         <v>157.3</v>
       </c>
       <c r="M96">
-        <v>99.8703</v>
+        <v>100.93275</v>
       </c>
       <c r="N96">
-        <v>57.42970000000001</v>
+        <v>56.36725</v>
       </c>
       <c r="O96">
-        <v>14.357425</v>
+        <v>14.0918125</v>
       </c>
       <c r="P96">
-        <v>43.072275</v>
+        <v>42.2754375</v>
       </c>
       <c r="Q96">
-        <v>88.27227500000001</v>
+        <v>87.4754375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6314138559369221</v>
+        <v>0.7462401021990642</v>
       </c>
       <c r="T96">
-        <v>11.73784500635572</v>
+        <v>14.03938324289606</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.575042830551225</v>
+        <v>1.558463432334896</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1014370051099532</v>
+        <v>0.101539178863691</v>
       </c>
       <c r="C97">
-        <v>-267.2117222788671</v>
+        <v>-280.4922754065337</v>
       </c>
       <c r="D97">
-        <v>804.9632777211331</v>
+        <v>803.4877245934665</v>
       </c>
       <c r="E97">
-        <v>614.6750000000002</v>
+        <v>626.4800000000002</v>
       </c>
       <c r="F97">
-        <v>1121.475</v>
+        <v>1133.28</v>
       </c>
       <c r="G97">
         <v>49.3</v>
@@ -9241,28 +9241,28 @@
         <v>157.3</v>
       </c>
       <c r="M97">
-        <v>100.93275</v>
+        <v>101.9952</v>
       </c>
       <c r="N97">
-        <v>56.36725</v>
+        <v>55.3048</v>
       </c>
       <c r="O97">
-        <v>14.0918125</v>
+        <v>13.8262</v>
       </c>
       <c r="P97">
-        <v>42.2754375</v>
+        <v>41.4786</v>
       </c>
       <c r="Q97">
-        <v>87.4754375</v>
+        <v>86.6786</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7462401021990642</v>
+        <v>0.9184794715922772</v>
       </c>
       <c r="T97">
-        <v>14.03938324289606</v>
+        <v>17.49169059770658</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.558463432334896</v>
+        <v>1.542229438248074</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.101539178863691</v>
+        <v>0.1016413526174289</v>
       </c>
       <c r="C98">
-        <v>-280.4922754065334</v>
+        <v>-293.7674288511763</v>
       </c>
       <c r="D98">
-        <v>803.4877245934666</v>
+        <v>802.0175711488238</v>
       </c>
       <c r="E98">
-        <v>626.48</v>
+        <v>638.2850000000001</v>
       </c>
       <c r="F98">
-        <v>1133.28</v>
+        <v>1145.085</v>
       </c>
       <c r="G98">
         <v>49.3</v>
@@ -9323,28 +9323,28 @@
         <v>157.3</v>
       </c>
       <c r="M98">
-        <v>101.9952</v>
+        <v>103.05765</v>
       </c>
       <c r="N98">
-        <v>55.30480000000001</v>
+        <v>54.24235000000002</v>
       </c>
       <c r="O98">
-        <v>13.8262</v>
+        <v>13.5605875</v>
       </c>
       <c r="P98">
-        <v>41.47860000000001</v>
+        <v>40.68176250000001</v>
       </c>
       <c r="Q98">
-        <v>86.67860000000002</v>
+        <v>85.88176250000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9184794715922748</v>
+        <v>1.205545087247629</v>
       </c>
       <c r="T98">
-        <v>17.49169059770653</v>
+        <v>23.24553618905736</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.542229438248075</v>
+        <v>1.526330165688816</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1016413526174289</v>
+        <v>0.1017435263711667</v>
       </c>
       <c r="C99">
-        <v>-293.7674288511763</v>
+        <v>-307.0372121983019</v>
       </c>
       <c r="D99">
-        <v>802.0175711488238</v>
+        <v>800.5527878016981</v>
       </c>
       <c r="E99">
-        <v>638.2850000000001</v>
+        <v>650.0899999999999</v>
       </c>
       <c r="F99">
-        <v>1145.085</v>
+        <v>1156.89</v>
       </c>
       <c r="G99">
         <v>49.3</v>
@@ -9405,28 +9405,28 @@
         <v>157.3</v>
       </c>
       <c r="M99">
-        <v>103.05765</v>
+        <v>104.1201</v>
       </c>
       <c r="N99">
-        <v>54.24235000000002</v>
+        <v>53.17990000000003</v>
       </c>
       <c r="O99">
-        <v>13.5605875</v>
+        <v>13.29497500000001</v>
       </c>
       <c r="P99">
-        <v>40.68176250000001</v>
+        <v>39.88492500000002</v>
       </c>
       <c r="Q99">
-        <v>85.88176250000001</v>
+        <v>85.08492500000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.205545087247629</v>
+        <v>1.779676318558336</v>
       </c>
       <c r="T99">
-        <v>23.24553618905736</v>
+        <v>34.75322737175903</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.526330165688816</v>
+        <v>1.510755368079747</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1017435263711667</v>
+        <v>0.1479857000964357</v>
       </c>
       <c r="C100">
-        <v>-307.0372121983019</v>
+        <v>-681.1169830795336</v>
       </c>
       <c r="D100">
-        <v>800.5527878016981</v>
+        <v>438.2780169204663</v>
       </c>
       <c r="E100">
-        <v>650.0899999999999</v>
+        <v>661.895</v>
       </c>
       <c r="F100">
-        <v>1156.89</v>
+        <v>1168.695</v>
       </c>
       <c r="G100">
         <v>49.3</v>
@@ -9487,129 +9487,47 @@
         <v>157.3</v>
       </c>
       <c r="M100">
-        <v>104.1201</v>
+        <v>171.564426</v>
       </c>
       <c r="N100">
-        <v>53.17990000000003</v>
+        <v>-14.26442599999999</v>
       </c>
       <c r="O100">
-        <v>13.29497500000001</v>
+        <v>-3.566106499999997</v>
       </c>
       <c r="P100">
-        <v>39.88492500000002</v>
+        <v>-10.69831949999999</v>
       </c>
       <c r="Q100">
-        <v>85.08492500000003</v>
+        <v>34.50168050000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.779676318558336</v>
+        <v>3.596585596259405</v>
       </c>
       <c r="T100">
-        <v>34.75322737175903</v>
+        <v>71.17073914347846</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.25</v>
+        <v>0.2292141845303058</v>
       </c>
       <c r="W100">
-        <v>0.0675</v>
+        <v>0.1131513577109511</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.510755368079747</v>
+        <v>0.9168567381212234</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1479857000964357</v>
-      </c>
-      <c r="C101">
-        <v>-681.1169830795336</v>
-      </c>
-      <c r="D101">
-        <v>438.2780169204663</v>
-      </c>
-      <c r="E101">
-        <v>661.895</v>
-      </c>
-      <c r="F101">
-        <v>1168.695</v>
-      </c>
-      <c r="G101">
-        <v>49.3</v>
-      </c>
-      <c r="H101">
-        <v>673.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>202.5</v>
-      </c>
-      <c r="K101">
-        <v>45.2</v>
-      </c>
-      <c r="L101">
-        <v>157.3</v>
-      </c>
-      <c r="M101">
-        <v>171.564426</v>
-      </c>
-      <c r="N101">
-        <v>-14.26442599999999</v>
-      </c>
-      <c r="O101">
-        <v>-3.566106499999997</v>
-      </c>
-      <c r="P101">
-        <v>-10.69831949999999</v>
-      </c>
-      <c r="Q101">
-        <v>34.50168050000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.596585596259405</v>
-      </c>
-      <c r="T101">
-        <v>71.17073914347846</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2292141845303058</v>
-      </c>
-      <c r="W101">
-        <v>0.1131513577109511</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9168567381212234</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
